--- a/Sanitary_Engineering_Exam_DB_v28.xlsx
+++ b/Sanitary_Engineering_Exam_DB_v28.xlsx
@@ -37252,7 +37252,7 @@
       </c>
       <c r="E282" s="52" t="inlineStr">
         <is>
-          <t>日照・日射・採光</t>
+          <t>照度・光環境</t>
         </is>
       </c>
       <c r="F282" s="52" t="n">
@@ -37260,37 +37260,38 @@
       </c>
       <c r="G282" s="53" t="inlineStr">
         <is>
-          <t>日射遮蔽、天空日照、直達日射量および窓ブラインド等による日射調整に関する正誤判定</t>
+          <t>点光源からの水平面照度計算</t>
         </is>
       </c>
       <c r="H282" s="53" t="inlineStr">
         <is>
-          <t>日照及び日射に関する次の記述のうち，最も不適切なものはどれか。</t>
+          <t>下図に示す点光源に照らされたＡ点の水平面照度に最も近い値はどれか。ただし，点光源の配光特性は一様なものとし，反射は考慮しないものとする。
+［条件：点光源（光度200cd）、高さ2m、照射角60°、A点］</t>
         </is>
       </c>
       <c r="I282" s="53" t="inlineStr">
         <is>
-          <t>① 大気圏外の太陽放射スペクトルは，赤外線域が最も大きく，可視光線や紫外線は含まれない。</t>
+          <t>① 6.3 lx</t>
         </is>
       </c>
       <c r="J282" s="53" t="inlineStr">
         <is>
-          <t>② 天空日射量は，太陽放射が大気中の空気分子や浮遊粒子によって散乱されて地表に届く量である。</t>
+          <t>② 8.3 lx</t>
         </is>
       </c>
       <c r="K282" s="53" t="inlineStr">
         <is>
-          <t>③ 直達日射量は，太陽から受照面に直接到達する太陽放射量である。</t>
+          <t>③ 10.8 lx</t>
         </is>
       </c>
       <c r="L282" s="53" t="inlineStr">
         <is>
-          <t>④ 南向き垂直面が受ける直達日射量は，冬至の正午頃に最大となる。</t>
+          <t>④ 12.5 lx</t>
         </is>
       </c>
       <c r="M282" s="53" t="inlineStr">
         <is>
-          <t>⑤ 外部日射遮蔽部材（ルーバー等）は，内部ブラインドよりも日射遮蔽効果が高い。</t>
+          <t>⑤ 50.0 lx</t>
         </is>
       </c>
     </row>
@@ -37317,7 +37318,7 @@
       </c>
       <c r="E283" s="52" t="inlineStr">
         <is>
-          <t>照度・光環境</t>
+          <t>温熱環境・室内温度分布</t>
         </is>
       </c>
       <c r="F283" s="52" t="n">
@@ -37325,37 +37326,37 @@
       </c>
       <c r="G283" s="53" t="inlineStr">
         <is>
-          <t>点光源からの水平面照度計算、グレア防止、昼光率および視環境・明視条件に関する正誤判定</t>
+          <t>室内の上下温度分布、日射・隙間風影響、上昇気流、居住域空調およびエアフローウィンドウ</t>
         </is>
       </c>
       <c r="H283" s="53" t="inlineStr">
         <is>
-          <t>光環境及び照明基本単位に関する次の記述のうち，最も不適切なものはどれか。</t>
+          <t>室内の温度分布に関する次の記述のうち，最も不適切なものはどれか。</t>
         </is>
       </c>
       <c r="I283" s="53" t="inlineStr">
         <is>
-          <t>① 照度（lx）は光源の明るさそのものを示し，光度（cd）は照射された面の明るさを示す。</t>
+          <t>① 良好な温熱環境を実現するためには，極端な室内温度分布が生じるのは好ましくないため，床上0.1mから1.1m間の上下温度分布は5℃以内に抑えるのが好ましい。</t>
         </is>
       </c>
       <c r="J283" s="53" t="inlineStr">
         <is>
-          <t>② 昼光率は，室内作業面照度の全天空照度に対する割合（%）である。</t>
+          <t>② 夏期に日射熱が室内へ侵入する場合や外気温が高い場合は，窓側の空気温度は室の奥よりも高くなり，冬期に隙間風が侵入する場合や外気温が低い場合は，窓側の空気温度は低くなる傾向にある。</t>
         </is>
       </c>
       <c r="K283" s="53" t="inlineStr">
         <is>
-          <t>③ 光束の単位はルーメン（lm）である。</t>
+          <t>③ 室内には種々の発熱体が存在し，近傍の空気温度を上昇させる。この高温空気は密度が小さいため，浮力により上昇気流が発生する場合がある。</t>
         </is>
       </c>
       <c r="L283" s="53" t="inlineStr">
         <is>
-          <t>④ グレアは，高輝度な光源が視野内に存在することで生じる不快感や視認性低下である。</t>
+          <t>④ 空調・換気設備は，床面より1.8m程度までの居住域を良好な温熱空気環境に保つことが目的であるが，室内に温度分布を生じさせる原因でもある。</t>
         </is>
       </c>
       <c r="M283" s="53" t="inlineStr">
         <is>
-          <t>⑤ タスク・アンビエント照明は，全般照明と局所照明を組み合わせて省エネを図る。</t>
+          <t>⑤ エアフローウィンドウは，2枚のガラスの間にブラインドを設けたもので，窓枠下部から室内空気を吸引し，これを窓上部から排気するものである。</t>
         </is>
       </c>
     </row>
@@ -37390,37 +37391,37 @@
       </c>
       <c r="G284" s="53" t="inlineStr">
         <is>
-          <t>壁体の熱伝達率、熱貫流率、熱伝導率および熱移動メカニズムに関する基本記述の正誤判定</t>
+          <t>材料の熱定数（中空層熱抵抗、グラスウール・畳・ALC・二重ガラスの熱伝導率・熱抵抗）</t>
         </is>
       </c>
       <c r="H284" s="53" t="inlineStr">
         <is>
-          <t>壁体の熱移動に関する次の記述のうち，最も不適切なものはどれか。</t>
+          <t>材料の熱定数に関する次の記述のうち，最も不適切なものはどれか。</t>
         </is>
       </c>
       <c r="I284" s="53" t="inlineStr">
         <is>
-          <t>① 熱伝導率は，物質固有の熱の伝えやすさを示す指標である。</t>
+          <t>① 中空層の熱抵抗は，熱流方向が下向きの方が上向きより大きい。</t>
         </is>
       </c>
       <c r="J284" s="53" t="inlineStr">
         <is>
-          <t>② 壁の熱抵抗は，熱伝導率に壁の厚さを乗じることで算出される。</t>
+          <t>② グラスウールの熱伝導率は，かさ比重が小さいほど小さくなる傾向がある。</t>
         </is>
       </c>
       <c r="K284" s="53" t="inlineStr">
         <is>
-          <t>③ 熱貫流率は，熱抵抗の逆数として計算される。</t>
+          <t>③ 畳の熱伝導率は，木材と同程度である。</t>
         </is>
       </c>
       <c r="L284" s="53" t="inlineStr">
         <is>
-          <t>④ 外断熱は，構造躯体を保温するため熱橋対策に有効である。</t>
+          <t>④ ALCの熱伝導率は，普通コンクリートの1／10程度である。</t>
         </is>
       </c>
       <c r="M284" s="53" t="inlineStr">
         <is>
-          <t>⑤ 中空層の熱抵抗は，放射と空気の対流伝熱によって決まる。</t>
+          <t>⑤ 二重ガラスなど密閉中空層の熱抵抗は，壁の中空層など半密閉中空層の2倍程度である。</t>
         </is>
       </c>
     </row>
@@ -37447,7 +37448,7 @@
       </c>
       <c r="E285" s="52" t="inlineStr">
         <is>
-          <t>遮音・音環境</t>
+          <t>日照・日射・採光</t>
         </is>
       </c>
       <c r="F285" s="52" t="n">
@@ -37455,37 +37456,37 @@
       </c>
       <c r="G285" s="53" t="inlineStr">
         <is>
-          <t>残響時間計算、空気音・床衝撃音遮音性能、コインシデンス効果および吸音機構に関する正誤判定</t>
+          <t>実効放射量、集合住宅の隣棟間隔係数、熱線吸収ガラス、直接昼光率および頂側窓</t>
         </is>
       </c>
       <c r="H285" s="53" t="inlineStr">
         <is>
-          <t>音環境に関する次の記述のうち，最も不適切なものはどれか。</t>
+          <t>日照・日射に関する次の記述のうち，最も不適切なものはどれか。</t>
         </is>
       </c>
       <c r="I285" s="53" t="inlineStr">
         <is>
-          <t>① 透過損失が大きい壁ほど，音をよく通しやすいことを意味する。</t>
+          <t>① 実効放射量（夜間放射量）は，雲があるときは，雲がないときに比較して増加する。</t>
         </is>
       </c>
       <c r="J285" s="53" t="inlineStr">
         <is>
-          <t>② 一重壁の空気音遮音は，面密度が大きいほど効果が高くなる（質量法則）。</t>
+          <t>② 東西に長い集合住宅において，東京で日照時間を4時間確保するための隣棟間隔係数（隣棟間隔d／建物高さh）は，2程度となる。</t>
         </is>
       </c>
       <c r="K285" s="53" t="inlineStr">
         <is>
-          <t>③ 残響時間は室容積に比例し，等価吸音面積に反比例する（サビンの式）。</t>
+          <t>③ 熱線吸収ガラスは，冷房時に効果がある。</t>
         </is>
       </c>
       <c r="L285" s="53" t="inlineStr">
         <is>
-          <t>④ 多孔質材料は，高音域の吸音に適している。</t>
+          <t>④ 対向建物などがない場合は，ガラスのない開放された窓では，近似的に直接昼光率と立体角投射率［%］は一致する。</t>
         </is>
       </c>
       <c r="M285" s="53" t="inlineStr">
         <is>
-          <t>⑤ 音の屈折現象は，空気中の温度勾配や風速分布によって生じる。</t>
+          <t>⑤ 頂側窓は，昼光によって展示品を鑑賞したい美術館の展示室や面積の大きい工場に用いられる。</t>
         </is>
       </c>
     </row>
@@ -37512,7 +37513,7 @@
       </c>
       <c r="E286" s="52" t="inlineStr">
         <is>
-          <t>結露・結露防止対策</t>
+          <t>遮音・音環境</t>
         </is>
       </c>
       <c r="F286" s="52" t="n">
@@ -37520,37 +37521,37 @@
       </c>
       <c r="G286" s="53" t="inlineStr">
         <is>
-          <t>内部結露・表面結露の発生メカニズムおよび断熱・防湿層設置等の防止対策に関する正誤判定</t>
+          <t>障壁の回折効果、残響時間、多孔質吸音材の吸音特性、重量衝撃音およびコインシデンス効果</t>
         </is>
       </c>
       <c r="H286" s="53" t="inlineStr">
         <is>
-          <t>結露現象及びその防止対策に関する次の記述のうち，最も不適切なものはどれか。</t>
+          <t>音環境に関する次の記述のうち，最も不適切なものはどれか。</t>
         </is>
       </c>
       <c r="I286" s="53" t="inlineStr">
         <is>
-          <t>① 表面結露は，壁面温度が室内空気の露点温度以下になると発生する。</t>
+          <t>① 障壁は，回折による高音域の遮断に対する効果が大きい。</t>
         </is>
       </c>
       <c r="J286" s="53" t="inlineStr">
         <is>
-          <t>② 内部結露は，壁体内部を拡散する水蒸気が冷やされることで生じる。</t>
+          <t>② 音響エネルギー密度が60dBだけ減衰するのに要する時間を残響時間という。</t>
         </is>
       </c>
       <c r="K286" s="53" t="inlineStr">
         <is>
-          <t>③ 冬期の結露防止用防湿層は，壁体の外気側（低温側）に設置する。</t>
+          <t>③ 多孔質材の吸音機構において，剛壁に直貼りしたときの吸音率は，吸音材の材厚を厚くしても，低音域の吸音率は向上しない。</t>
         </is>
       </c>
       <c r="L286" s="53" t="inlineStr">
         <is>
-          <t>④ 断熱性の向上は，壁体内表面温度を高めて表面結露を防ぐ。</t>
+          <t>④ 重量衝撃音の低減に対しては，床構造の曲げ剛性や質量が重要で，木造などの軽量床の場合，必要な性能を得ることは困難である。</t>
         </is>
       </c>
       <c r="M286" s="53" t="inlineStr">
         <is>
-          <t>⑤ 換気により室内の水蒸気圧を下げることが有効である。</t>
+          <t>⑤ コインシデンス効果は，音がさまざまな方向から壁面に入射する場合には広い周波数で発生する。</t>
         </is>
       </c>
     </row>
@@ -37577,7 +37578,7 @@
       </c>
       <c r="E287" s="52" t="inlineStr">
         <is>
-          <t>日射・熱移動</t>
+          <t>換気・自然換気</t>
         </is>
       </c>
       <c r="F287" s="52" t="n">
@@ -37585,37 +37586,37 @@
       </c>
       <c r="G287" s="53" t="inlineStr">
         <is>
-          <t>日射遮蔽、天空日照、直達日射量および窓ブラインド等による日射調整に関する正誤判定</t>
+          <t>自然換気（開口部通過風量、実効面積・流量係数、中性帯位置、風圧係数、温度差換気量）</t>
         </is>
       </c>
       <c r="H287" s="53" t="inlineStr">
         <is>
-          <t>空調熱負荷に関する次の記述のうち，最も不適切なものはどれか。</t>
+          <t>自然換気に関する次の記述のうち，最も不適切なものはどれか。</t>
         </is>
       </c>
       <c r="I287" s="53" t="inlineStr">
         <is>
-          <t>① 顕熱負荷は温度上昇・下降を伴う熱負荷である。</t>
+          <t>① 窓を開放した場合などの開口部通過風量は，開口部面積に比例し，圧力差の平方根に比例する。</t>
         </is>
       </c>
       <c r="J287" s="53" t="inlineStr">
         <is>
-          <t>② 潜熱負荷は状態変化（湿度変化）を伴う熱負荷である。</t>
+          <t>② 実効面積αAにおけるαは流量係数であり，開口の形状や寸法で異なるが，通常端部が直角に整形された窓では0.6〜0.7程度となる。</t>
         </is>
       </c>
       <c r="K287" s="53" t="inlineStr">
         <is>
-          <t>③ 外気負荷は，導入外気を室内状態まで加熱・冷却・加減湿する負荷である。</t>
+          <t>③ 中性帯の位置は，定性的には開口部の大きい方に近づく。</t>
         </is>
       </c>
       <c r="L287" s="53" t="inlineStr">
         <is>
-          <t>④ 躯体の蓄熱効果は熱負荷のピーク値を著しく引き上げる要因となる。</t>
+          <t>④ 2つの開口部があるとき，2つの開口部とも負の風圧係数となる場合，それらの風圧係数に差があっても風力換気は生じない。</t>
         </is>
       </c>
       <c r="M287" s="53" t="inlineStr">
         <is>
-          <t>⑤ 人体からの放熱には，顕熱放熱と潜熱放熱の両方が含まれる。</t>
+          <t>⑤ 高さの異なる2つの開口部があるときの温度差換気量は，直列合成した実効面積αAに比例するとともに，室内外温度差及び開口高さの差の平方根に比例して増加する。</t>
         </is>
       </c>
     </row>
@@ -37642,7 +37643,7 @@
       </c>
       <c r="E288" s="52" t="inlineStr">
         <is>
-          <t>温熱環境・温熱指標(PMV/WBGT)</t>
+          <t>水配管・ポンプ</t>
         </is>
       </c>
       <c r="F288" s="52" t="n">
@@ -37650,37 +37651,37 @@
       </c>
       <c r="G288" s="53" t="inlineStr">
         <is>
-          <t>作用温度(OT)、PMV、WBGT、新有効温度(ET*)等の温熱環境指標に関する記述の正誤判定</t>
+          <t>水配管（開放式・密閉式ポンプ動力、二方弁・三方弁制御、管摩擦抵抗、リバースリターン、管内流速）</t>
         </is>
       </c>
       <c r="H288" s="53" t="inlineStr">
         <is>
-          <t>温熱環境指標に関する次の記述のうち，最も不適切なものはどれか。</t>
+          <t>水配管に関する次の記述のうち，最も不適切なものはどれか。</t>
         </is>
       </c>
       <c r="I288" s="53" t="inlineStr">
         <is>
-          <t>① PMV は熱中症のみを評価する専門指標である。</t>
+          <t>① 開放式は必ず摩擦抵抗のほかに押し上げ揚程が加わり，密閉式に比べてポンプ動力が大きくなる。</t>
         </is>
       </c>
       <c r="J288" s="53" t="inlineStr">
         <is>
-          <t>② 作用温度（OT）は，気温と放射温度を考慮した指標である。</t>
+          <t>② 二方弁制御は三方弁制御に比べて一般に制御性が良く，ポンプの台数制御などによりポンプの消費電力を節約できる。</t>
         </is>
       </c>
       <c r="K288" s="53" t="inlineStr">
         <is>
-          <t>③ WBGT（暑さ指数）は，屋外では湿球温度・黒球温度・乾球温度から算出される。</t>
+          <t>③ 満水状態で流体が流れる場合の直管部摩擦抵抗は，管の長さと流体の密度及び流速の2乗に比例し，管の内径と管摩擦係数に反比例する。</t>
         </is>
       </c>
       <c r="L288" s="53" t="inlineStr">
         <is>
-          <t>④ 新有効温度（ET*）は相対湿度50%を基準とする指標である。</t>
+          <t>④ リバースリターン方式では，各機器を通る配管長さが等しく，抵抗が同じとなるために，流量が自然に均一になるという特徴がある。</t>
         </is>
       </c>
       <c r="M288" s="53" t="inlineStr">
         <is>
-          <t>⑤ 代謝量（met）や着衣量（clo）はPMVの入力要素である。</t>
+          <t>⑤ 普通の屋内配管では，侵食を防ぐための管内流速を一般に2.0m／s以下としている。</t>
         </is>
       </c>
     </row>
@@ -37707,7 +37708,7 @@
       </c>
       <c r="E289" s="52" t="inlineStr">
         <is>
-          <t>湿気環境・比エンタルピー</t>
+          <t>省エネルギーシステム</t>
         </is>
       </c>
       <c r="F289" s="52" t="n">
@@ -37715,37 +37716,37 @@
       </c>
       <c r="G289" s="53" t="inlineStr">
         <is>
-          <t>建築環境・空調・給排水における技術基準および正誤判定</t>
+          <t>省エネルギー設備（全熱交換器バイパス、蓄熱槽システム、コージェネレーション、太陽電池、COP定義）</t>
         </is>
       </c>
       <c r="H289" s="53" t="inlineStr">
         <is>
-          <t>空気線図に関する次の記述のうち，最も不適切なものはどれか。</t>
+          <t>省エネルギー設備機器に関する次の記述のうち，最も不適切なものはどれか。</t>
         </is>
       </c>
       <c r="I289" s="53" t="inlineStr">
         <is>
-          <t>① 乾球温度と絶対湿度が決まれば，空気の状態点が定まる。</t>
+          <t>① 空気調和機に使用する全熱交換器では，外気冷房が可能なときに給排気バイパスなどにより熱交換を回避する。</t>
         </is>
       </c>
       <c r="J289" s="53" t="inlineStr">
         <is>
-          <t>② 相対湿度は，水蒸気分圧の飽和水蒸気圧に対する割合である。</t>
+          <t>② 夜間電力利用の蓄熱槽システムでは，熱源の夜間運転時間が長いほど，熱源容量は小さくて済む。</t>
         </is>
       </c>
       <c r="K289" s="53" t="inlineStr">
         <is>
-          <t>③ 加熱コイルでの加熱では，絶対湿度は変化しない。</t>
+          <t>③ コージェネレーションシステムは，ガスタービンやガスエンジン，燃料電池などを用いて電力エネルギーと熱エネルギーの両者を同時に供給するシステムであり，総合効率は最大80%程度まで期待することができる。</t>
         </is>
       </c>
       <c r="L289" s="53" t="inlineStr">
         <is>
-          <t>④ 冷却減湿では，空気が露点以下まで冷却される。</t>
+          <t>④ 多結晶シリコン太陽電池は，単結晶シリコン太陽電池と比較して変換効率が低いが，製造が容易で効率とコストのバランスが良いため，よく普及している太陽電池である。</t>
         </is>
       </c>
       <c r="M289" s="53" t="inlineStr">
         <is>
-          <t>⑤ 水噴霧加湿では，空気の乾球温度が急激に上昇する。</t>
+          <t>⑤ ヒートポンプの冷房時の成績係数（COP）は，圧縮仕事に対する凝縮熱量の比で表す。</t>
         </is>
       </c>
     </row>
@@ -37772,7 +37773,7 @@
       </c>
       <c r="E290" s="52" t="inlineStr">
         <is>
-          <t>室内機器・顕熱発熱</t>
+          <t>給水設備</t>
         </is>
       </c>
       <c r="F290" s="52" t="n">
@@ -37780,37 +37781,37 @@
       </c>
       <c r="G290" s="53" t="inlineStr">
         <is>
-          <t>建築環境・空調・給排水における技術基準および正誤判定</t>
+          <t>給水設備（高置水槽容量、受水槽有効容量、貯水槽点検スペース、クロスコネクション、給水圧力上限）</t>
         </is>
       </c>
       <c r="H290" s="53" t="inlineStr">
         <is>
-          <t>室内発生熱量に関する次の記述のうち，最も不適切なものはどれか。</t>
+          <t>給水設備に関する次の記述のうち，最も不適切なものはどれか。</t>
         </is>
       </c>
       <c r="I290" s="53" t="inlineStr">
         <is>
-          <t>① 室温が高くなると，人体からの放熱は潜熱量が減少し顕熱量が増加する。</t>
+          <t>① 高置水槽容量は，揚水ポンプの能力との関係によっても異なるが，一般に1日の使用水量の1／3程度とすることが多い。</t>
         </is>
       </c>
       <c r="J290" s="53" t="inlineStr">
         <is>
-          <t>② OA機器の発熱は，主に顕熱負荷となる。</t>
+          <t>② 受水槽の有効容量は，水道事業者が断水を考慮して指定要綱などで設計用給水量の4／10〜6／10程度の容量を確保するところが多く，概算で1日の使用水量の1／2程度としている。</t>
         </is>
       </c>
       <c r="K290" s="53" t="inlineStr">
         <is>
-          <t>③ 白熱灯は入力電力の大部分が熱となる。</t>
+          <t>③ 貯水槽はすべての面から点検できるように水槽の上面に1.0m以上，側面と下面に0.6m以上の空間を確保して設置する。</t>
         </is>
       </c>
       <c r="L290" s="53" t="inlineStr">
         <is>
-          <t>④ 顕熱比（SHF）は，全熱負荷に対する顕熱負荷の割合である。</t>
+          <t>④ 井戸を使っている住宅などで，井戸水の配管と水道配管を接続させることはクロスコネクションとなる。</t>
         </is>
       </c>
       <c r="M290" s="53" t="inlineStr">
         <is>
-          <t>⑤ 厨房機器の燃焼ガスには水蒸気（潜熱）が含まれる。</t>
+          <t>⑤ 一般に給水管の給水圧力の上限値は，ホテル・集合住宅で300〜400kPa程度，事務所・工場では400〜500kPa程度として計画する。</t>
         </is>
       </c>
     </row>
@@ -37837,7 +37838,7 @@
       </c>
       <c r="E291" s="52" t="inlineStr">
         <is>
-          <t>パーソナル空調・空調方式</t>
+          <t>ポンプ・ファン</t>
         </is>
       </c>
       <c r="F291" s="52" t="n">
@@ -37845,37 +37846,37 @@
       </c>
       <c r="G291" s="53" t="inlineStr">
         <is>
-          <t>VAV方式、床吹出し空調、全熱交換器、パッケージ空調等の方式比較と特徴に関する正誤判定</t>
+          <t>ポンプ及びファン（ラインポンプ、クロスフローファン、遠心ポンプ諸特性、シロッコ/ターボファン、渦巻きポンプ固定案内羽根）</t>
         </is>
       </c>
       <c r="H291" s="53" t="inlineStr">
         <is>
-          <t>空調方式に関する次の記述のうち，最も不適切なものはどれか。</t>
+          <t>ポンプ及びファンに関する次の記述のうち，最も不適切なものはどれか。</t>
         </is>
       </c>
       <c r="I291" s="53" t="inlineStr">
         <is>
-          <t>① CAV（定風量）方式は，送風量を一定に保つ。</t>
+          <t>① ラインポンプは小規模な冷温水循環用として配管途中に直接取り付けられるものである。</t>
         </is>
       </c>
       <c r="J291" s="53" t="inlineStr">
         <is>
-          <t>② VAV（変風量）方式は，負荷に応じて風量を制御する。</t>
+          <t>② クロスフローファンはエアコン，ファンコイルユニット，室内空気のサーキュレーターなど機器組込みの低圧ファンとして利用されている。</t>
         </is>
       </c>
       <c r="K291" s="53" t="inlineStr">
         <is>
-          <t>③ 水―空気方式は，ダクトスペースを縮小できる。</t>
+          <t>③ 遠心ポンプの流量と揚程は羽根車の毎分回転数で変化するが，流量は回転数に比例し，揚程は回転数の2乗に比例する。また，軸動力は回転数の3乗に比例する。</t>
         </is>
       </c>
       <c r="L291" s="53" t="inlineStr">
         <is>
-          <t>④ 個別方式は，各ゾーンでの独立運転が容易である。</t>
+          <t>④ 空調用の送風機は高い省エネルギー性を求める場合，多翼型のシロッコファンよりも効率の高い後曲型のターボファンを使用する例が増えている。</t>
         </is>
       </c>
       <c r="M291" s="53" t="inlineStr">
         <is>
-          <t>⑤ 全空気方式は，水方式に比べてダクト寸法を極めて小さくできる。</t>
+          <t>⑤ 渦巻きポンプには羽根車の外に流れの乱れを防ぎポンプ効率を改善するための固定案内羽根がある。</t>
         </is>
       </c>
     </row>
@@ -37902,7 +37903,7 @@
       </c>
       <c r="E292" s="52" t="inlineStr">
         <is>
-          <t>省エネルギーシステム・BEMS</t>
+          <t>ボイラー設備</t>
         </is>
       </c>
       <c r="F292" s="52" t="n">
@@ -37910,37 +37911,37 @@
       </c>
       <c r="G292" s="53" t="inlineStr">
         <is>
-          <t>建築環境・空調・給排水における技術基準および正誤判定</t>
+          <t>ボイラー（ボイラー容量・単位、真空式温水機、貫流式ボイラー、鋳鉄製ボイラー、都市ガス燃料）</t>
         </is>
       </c>
       <c r="H292" s="53" t="inlineStr">
         <is>
-          <t>空調省エネ技術に関する次の記述のうち，最も不適切なものはどれか。</t>
+          <t>ボイラーに関する次の記述のうち，最も不適切なものはどれか。</t>
         </is>
       </c>
       <c r="I292" s="53" t="inlineStr">
         <is>
-          <t>① 全熱交換器は，排気の熱と湿度を回収する。</t>
+          <t>① ボイラーの容量は，定格出力すなわち最大連続負荷における毎時出力によって表され，蒸気ボイラーの場合は換算蒸発量［kg／h］又は実際蒸発量［kg／h］，温水ボイラーの場合は熱出力［kW］で表すのが通常である。</t>
         </is>
       </c>
       <c r="J292" s="53" t="inlineStr">
         <is>
-          <t>② 外気冷房は，中間期等の冷涼な外気を冷房に利用する。</t>
+          <t>② 真空式温水機は，鋼板製若しくは鋳鉄製のボイラーの大きな蒸気室に熱交換用のコイルをいくつか配置し，ボイラー内部の蒸気で間接的に暖房用水，給湯用水，プールの水などいくつかの系統の温水を1つのボイラーで加熱するものである。</t>
         </is>
       </c>
       <c r="K292" s="53" t="inlineStr">
         <is>
-          <t>③ VWVシステムは，冷温水流量をインバータ制御する。</t>
+          <t>③ 貫流式ボイラーは，燃焼室を取り巻く水管を給水が通過する間に，完全に蒸発する比較的小容量の蒸気ボイラーで，構造が簡単で効率も高く，安価なためにビルや工場などで用いられる。</t>
         </is>
       </c>
       <c r="L292" s="53" t="inlineStr">
         <is>
-          <t>④ BEMSは，手動バルブの開閉のみを記録する簡易記録計である。</t>
+          <t>④ 鋳鉄製ボイラーは大容量の高圧型ボイラーで，排気ガスによる給水加熱器又は燃焼空気予熱器などを用いるためボイラー効率は高く，大規模ビルや地域冷暖房プラントなどで用いられる。</t>
         </is>
       </c>
       <c r="M292" s="53" t="inlineStr">
         <is>
-          <t>⑤ 蓄熱システムは，夜間電力を利用して熱エネルギーを蓄える。</t>
+          <t>⑤ ボイラーの排気ガスは地方自治体によってSOx，NOx，煤塵量などが規制されており，市街地でのボイラーの燃料は都市ガスを採用することが多い。</t>
         </is>
       </c>
     </row>
@@ -37967,7 +37968,7 @@
       </c>
       <c r="E293" s="52" t="inlineStr">
         <is>
-          <t>給水設備・給水圧力</t>
+          <t>防災・消火設備</t>
         </is>
       </c>
       <c r="F293" s="52" t="n">
@@ -37975,37 +37976,37 @@
       </c>
       <c r="G293" s="53" t="inlineStr">
         <is>
-          <t>建築環境・空調・給排水における技術基準および正誤判定</t>
+          <t>消火設備（火災分類A〜D、消防設備区分、屋内消火栓放水圧力、屋外消火栓有効階、ドレンチャー設備）</t>
         </is>
       </c>
       <c r="H293" s="53" t="inlineStr">
         <is>
-          <t>給水設備に関する次の記述のうち，最も不適切なものはどれか。</t>
+          <t>消火設備に関する次の記述のうち，最も不適切なものはどれか。</t>
         </is>
       </c>
       <c r="I293" s="53" t="inlineStr">
         <is>
-          <t>① 直結増圧方式は受水槽を置かずに直接給水する。</t>
+          <t>① 火災は，A火災（普通火災），B火災（油火災），C火災（電気火災），D火災（金属火災）に区分される。</t>
         </is>
       </c>
       <c r="J293" s="53" t="inlineStr">
         <is>
-          <t>② クロスコネクションは飲用配管と他系統の誤接続で禁止されている。</t>
+          <t>② 消防の用に供する設備は，消火設備，警報設備，避難設備の3つに分類される。</t>
         </is>
       </c>
       <c r="K293" s="53" t="inlineStr">
         <is>
-          <t>③ ウォーターハンマーは静かな流速変化時に発生する現象である。</t>
+          <t>③ 屋内消火栓設備のホース先端における放水圧力は7MPaを超えないように規定されている。</t>
         </is>
       </c>
       <c r="L293" s="53" t="inlineStr">
         <is>
-          <t>④ バキュームブレーカは逆流（サイホン作用）を防ぐ。</t>
+          <t>④ 屋外消火栓設備は，1階及び2階の床面積の広い建物に設置し，屋外から屋内に向けて放水によって消火する設備であり，1階及び2階の部分に限って有効な消火設備である。</t>
         </is>
       </c>
       <c r="M293" s="53" t="inlineStr">
         <is>
-          <t>⑤ 吐水口空間は，給水栓と水受けあふれ面との間の空間である。</t>
+          <t>⑤ ドレンチャー消火設備は，建物外部の火災に対し外壁，屋根，開口部に水幕をつくって延焼を防ぐための設備である。</t>
         </is>
       </c>
     </row>
@@ -38032,7 +38033,7 @@
       </c>
       <c r="E294" s="52" t="inlineStr">
         <is>
-          <t>排水・通気配管・トラップ</t>
+          <t>結露・結露防止対策</t>
         </is>
       </c>
       <c r="F294" s="52" t="n">
@@ -38040,37 +38041,37 @@
       </c>
       <c r="G294" s="53" t="inlineStr">
         <is>
-          <t>建築環境・空調・給排水における技術基準および正誤判定</t>
+          <t>住宅の断熱・結露防止（夏型結露、通気構法・防風層、防湿層位置、材料内水蒸気移動、湿気伝導率）</t>
         </is>
       </c>
       <c r="H294" s="53" t="inlineStr">
         <is>
-          <t>排水通気設備に関する次の記述のうち，最も不適切なものはどれか。</t>
+          <t>戸建て住宅の断熱と結露防止に関する次の記述のうち，最も不適切なものはどれか。</t>
         </is>
       </c>
       <c r="I294" s="53" t="inlineStr">
         <is>
-          <t>① トラップの封水深は 50〜100mm である。</t>
+          <t>① 夏型結露は，構造用合板や外壁材に含まれている水分が日射で加熱され，壁体内を透過して防湿層裏面で結露する現象などをいう。</t>
         </is>
       </c>
       <c r="J294" s="53" t="inlineStr">
         <is>
-          <t>② 自己サイホン作用は満管流排水により生じる。</t>
+          <t>② 繊維状の断熱材を用いた外壁の通気構法には，断熱材内に冷たい外気が侵入しないよう，防風層の設置が必要である。</t>
         </is>
       </c>
       <c r="K294" s="53" t="inlineStr">
         <is>
-          <t>③ 通気管の主な目的は配管を保温して結露を防ぐことのみである。</t>
+          <t>③ 冬季の結露を防止するために，壁体内に設ける防湿層は，温度の低い，断熱材の外気側に配置しなくてはならない。</t>
         </is>
       </c>
       <c r="L294" s="53" t="inlineStr">
         <is>
-          <t>④ 各個通気方式は，最も高い通気性能をもつ。</t>
+          <t>④ 材料内の湿気移動は，含湿率があまり高く見られない場合には水蒸気の形で行われ，水蒸気圧の高い方から低い方へ流れる。</t>
         </is>
       </c>
       <c r="M294" s="53" t="inlineStr">
         <is>
-          <t>⑤ 二重トラップは排水障害を起こすため禁じられる。</t>
+          <t>⑤ 均質でない建築材料の湿気伝導率λ'を，透湿係数Pと厚さδから逆算してはならない。</t>
         </is>
       </c>
     </row>
@@ -38097,7 +38098,7 @@
       </c>
       <c r="E295" s="52" t="inlineStr">
         <is>
-          <t>封水損失・排水設備</t>
+          <t>加湿・除湿装置</t>
         </is>
       </c>
       <c r="F295" s="52" t="n">
@@ -38105,37 +38106,37 @@
       </c>
       <c r="G295" s="53" t="inlineStr">
         <is>
-          <t>建築環境・空調・給排水における技術基準および正誤判定</t>
+          <t>加湿器の各種方式（パン形、気化式、スプレー形、遠心加湿器、超音波加湿器）の特徴と正誤判定</t>
         </is>
       </c>
       <c r="H295" s="53" t="inlineStr">
         <is>
-          <t>排水配管に関する次の記述のうち，最も不適切なものはどれか。</t>
+          <t>加湿器に関する次の記述のうち，最も不適切なものはどれか。</t>
         </is>
       </c>
       <c r="I295" s="53" t="inlineStr">
         <is>
-          <t>① 間接排水は衛生上重要な機器の排水口に適用される。</t>
+          <t>① パン形加湿器は，水中に溶けた不純物が濃縮されるため，スケールが付着し，寿命が短い。</t>
         </is>
       </c>
       <c r="J295" s="53" t="inlineStr">
         <is>
-          <t>② 排水槽の底には勾配を設けて汚泥滞留を防ぐ。</t>
+          <t>② 気化式加湿器には，加湿装置についた残留物の洗浄用に加湿量の1.5〜3倍の給水量が必要である。</t>
         </is>
       </c>
       <c r="K295" s="53" t="inlineStr">
         <is>
-          <t>③ グリーストラップは油脂分を捕集する。</t>
+          <t>③ スプレー形加湿器は，水や温水噴霧の場合には温度低下を伴う。</t>
         </is>
       </c>
       <c r="L295" s="53" t="inlineStr">
         <is>
-          <t>④ 排水横管には適切な勾配を確保する。</t>
+          <t>④ 遠心加湿器は，水を回転拡散させ，霧状にして給湿する。</t>
         </is>
       </c>
       <c r="M295" s="53" t="inlineStr">
         <is>
-          <t>⑤ 雨水管と汚水管は建物のすべての場所で合流接続する。</t>
+          <t>⑤ 超音波加湿器は，常温で霧化するため，冷房時より暖房時の加湿に適する。</t>
         </is>
       </c>
     </row>
@@ -38162,7 +38163,7 @@
       </c>
       <c r="E296" s="52" t="inlineStr">
         <is>
-          <t>換気方式・換気量</t>
+          <t>室内環境・化学物質</t>
         </is>
       </c>
       <c r="F296" s="52" t="n">
@@ -38170,37 +38171,38 @@
       </c>
       <c r="G296" s="53" t="inlineStr">
         <is>
-          <t>建物開口部や室温差・風力による換気量・換気回数計算および給排気方式の正誤判定</t>
+          <t>ホルムアルデヒド放散速度の計算（室容積30m³、換気回数0.5/h、外気濃度5μg/m³、室内定常濃度20μg/m³、面積25m²）</t>
         </is>
       </c>
       <c r="H296" s="53" t="inlineStr">
         <is>
-          <t>換気計算及び給排気に関する次の記述のうち，最も不適切なものはどれか。</t>
+          <t>室内において，ホルムアルデヒドが単一の材料から放散するとき，下記の条件における材料の放散速度に最も近いものはどれか。ただし，材料の放散速度は気中濃度の影響を受けないものとし，発生したホルムアルデヒドは，瞬時に一様拡散し，吸着・分解せず，室内濃度に変動はなく安定しているものとする。
+条件：（1）室の容積：30m³、（2）室の換気回数：0.5回／h、（3）外気中のホルムアルデヒド濃度：5μg／m³、（4）室内空気中のホルムアルデヒド定常濃度：20μg／m³、（5）ホルムアルデヒド放散面積：25m²</t>
         </is>
       </c>
       <c r="I296" s="53" t="inlineStr">
         <is>
-          <t>① 必要換気量は CO2 発生量等から計算できる。</t>
+          <t>① 6 μg／m²h</t>
         </is>
       </c>
       <c r="J296" s="53" t="inlineStr">
         <is>
-          <t>② 第2種換気は，排気ファンのみを用いて室内を負圧にする。</t>
+          <t>② 9 μg／m²h</t>
         </is>
       </c>
       <c r="K296" s="53" t="inlineStr">
         <is>
-          <t>③ 第3種換気は，厨房やトイレ等の汚染・臭気源に適する。</t>
+          <t>③ 12 μg／m²h</t>
         </is>
       </c>
       <c r="L296" s="53" t="inlineStr">
         <is>
-          <t>④ 温度差換気量は，高低差と温度差に依存する。</t>
+          <t>④ 18 μg／m²h</t>
         </is>
       </c>
       <c r="M296" s="53" t="inlineStr">
         <is>
-          <t>⑤ 風力換気量は，風速と開口面積に比例する。</t>
+          <t>⑤ 21 μg／m²h</t>
         </is>
       </c>
     </row>
@@ -38227,7 +38229,7 @@
       </c>
       <c r="E297" s="52" t="inlineStr">
         <is>
-          <t>オゾン・室内空気質</t>
+          <t>ヒートアイランド現象</t>
         </is>
       </c>
       <c r="F297" s="52" t="n">
@@ -38235,37 +38237,37 @@
       </c>
       <c r="G297" s="53" t="inlineStr">
         <is>
-          <t>建築環境・空調・給排水における技術基準および正誤判定</t>
+          <t>ヒートアイランド現象（原因、ダストドーム形成、光化学オキシダント・集中豪雨、生物多様性・媒介生物、冬季暖房影響）</t>
         </is>
       </c>
       <c r="H297" s="53" t="inlineStr">
         <is>
-          <t>室内有害ガスに関する次の記述のうち，最も不適切なものはどれか。</t>
+          <t>ヒートアイランド現象の原因とその影響に関する次の記述のうち，最も不適切なものはどれか。</t>
         </is>
       </c>
       <c r="I297" s="53" t="inlineStr">
         <is>
-          <t>① CO（一酸化炭素）は，中毒を引き起こす有害ガスである。</t>
+          <t>① ヒートアイランド現象の原因としては，人工排熱の増加，緑地・水面の減少と地表面の人工化，都市形態の高密度化が挙げられる。</t>
         </is>
       </c>
       <c r="J297" s="53" t="inlineStr">
         <is>
-          <t>② CO2 は，有毒ガスであり微量でも即死に至る。</t>
+          <t>② ヒートアイランド現象による都市域の高温化により発生する上昇気流が温度層に遮られて生じる混合層（ダストドーム）を形成することが指摘されている。</t>
         </is>
       </c>
       <c r="K297" s="53" t="inlineStr">
         <is>
-          <t>③ ホルムアルデヒドは，建材や接着剤から放散される。</t>
+          <t>③ ヒートアイランド現象は，光化学オキシダント生成を助長するほか，局地的集中豪雨との関連性も指摘されている。</t>
         </is>
       </c>
       <c r="L297" s="53" t="inlineStr">
         <is>
-          <t>④ ラドンは，自然放射性物質である。</t>
+          <t>④ ヒートアイランド現象は，都市部における生物多様性に影響を与える可能性があり，感染症を媒介する生物の分布・個体数の変化などによる影響も懸念される。</t>
         </is>
       </c>
       <c r="M297" s="53" t="inlineStr">
         <is>
-          <t>⑤ 浮遊粉塵は，呼吸器に及ぼす影響が懸念される。</t>
+          <t>⑤ ヒートアイランド現象は，冬季においては大都市部を中心として気温の上昇が顕著であり，暖房エネルギーを削減する影響も報告されている。</t>
         </is>
       </c>
     </row>
@@ -38292,7 +38294,7 @@
       </c>
       <c r="E298" s="52" t="inlineStr">
         <is>
-          <t>ホルムアルデヒド放散速度・濃度</t>
+          <t>ねずみ・害虫対策</t>
         </is>
       </c>
       <c r="F298" s="52" t="n">
@@ -38300,37 +38302,37 @@
       </c>
       <c r="G298" s="53" t="inlineStr">
         <is>
-          <t>建築環境・空調・給排水における技術基準および正誤判定</t>
+          <t>建築物におけるねずみ・害虫対策（ねずみ駆除基本、ゴキブリ体内時計、ハエ類発生源、ダニのアレルゲン、昆虫侵入）</t>
         </is>
       </c>
       <c r="H298" s="53" t="inlineStr">
         <is>
-          <t>建築物衛生法基準に関する次の記述のうち，最も不適切なものはどれか。</t>
+          <t>建築物におけるねずみ・害虫対策に関する次の記述のうち，最も不適切なものはどれか。</t>
         </is>
       </c>
       <c r="I298" s="53" t="inlineStr">
         <is>
-          <t>① 浮遊粉塵は 0.15 mg/m3 以下である。</t>
+          <t>① ねずみの駆除は，餌を断つこと，通路を遮断すること，巣を作らせないことを基本に進める。</t>
         </is>
       </c>
       <c r="J298" s="53" t="inlineStr">
         <is>
-          <t>② 一酸化炭素は 10 ppm（特例20ppm）以下である。</t>
+          <t>② ゴキブリは，夜間，潜伏場所から出現し，摂食，摂水行動を起こし，体内に組み込まれた体内時計により，約24時間を周期とする行動がみられる。</t>
         </is>
       </c>
       <c r="K298" s="53" t="inlineStr">
         <is>
-          <t>③ 二酸化炭素は 10000 ppm 以下である。</t>
+          <t>③ イエバエ，クロバエ，ニクバエ類等の中・大型のハエ類は，厨房等の処理が適切に行われていても，幼虫が発生する。</t>
         </is>
       </c>
       <c r="L298" s="53" t="inlineStr">
         <is>
-          <t>④ 気流は 0.5 m/s 以下である。</t>
+          <t>④ 居住環境で見られるコナヒョウヒダニやヤケヒョウヒダニは，ヒトを刺したり吸血したりすることはないが，そのふんや死骸は喘息やアトピー性皮膚炎の原因となることがある。</t>
         </is>
       </c>
       <c r="M298" s="53" t="inlineStr">
         <is>
-          <t>⑤ 温度・湿度の望ましい範囲が設定されている。</t>
+          <t>⑤ 外気温が低くなると，外壁に内部から伝わる熱や，隙間から漏れる熱を感じて，越冬等の目的で昆虫等が侵入しやすくなる。</t>
         </is>
       </c>
     </row>
@@ -38357,7 +38359,7 @@
       </c>
       <c r="E299" s="52" t="inlineStr">
         <is>
-          <t>BOD測定・BOD容積負荷計算</t>
+          <t>水質指標・用語単位</t>
         </is>
       </c>
       <c r="F299" s="52" t="n">
@@ -38365,37 +38367,37 @@
       </c>
       <c r="G299" s="53" t="inlineStr">
         <is>
-          <t>流入水量・BOD濃度・ばっ気槽容量に基づくBOD容積負荷およびHRT/BOD-MLSS負荷の定型計算</t>
+          <t>生活排水処理施設の用語と単位の組合せ（水面積負荷、ばっ気強度、越流負荷、比表面積、BOD-MLSS負荷）</t>
         </is>
       </c>
       <c r="H299" s="53" t="inlineStr">
         <is>
-          <t>水質濁度・汚濁指標に関する次の記述のうち，最も不適切なものはどれか。</t>
+          <t>生活排水処理施設の設計又は維持管理において用いられる用語と単位の組合せとして，次のうち最も不適切なものはどれか。</t>
         </is>
       </c>
       <c r="I299" s="53" t="inlineStr">
         <is>
-          <t>① BOD は好気性微生物による酸素消費量である。</t>
+          <t>① 水面積負荷 ── m³／(m²・日)</t>
         </is>
       </c>
       <c r="J299" s="53" t="inlineStr">
         <is>
-          <t>② COD は化学酸化剤による酸素要求量である。</t>
+          <t>② ばっ気強度 ── m³／(m³・時)</t>
         </is>
       </c>
       <c r="K299" s="53" t="inlineStr">
         <is>
-          <t>③ SS は溶解しているすべての塩分濃度を示す。</t>
+          <t>③ 越流負荷 ── m³／(m²・時)</t>
         </is>
       </c>
       <c r="L299" s="53" t="inlineStr">
         <is>
-          <t>④ TOC は全有機炭素量である。</t>
+          <t>④ 比表面積 ── m²／m³</t>
         </is>
       </c>
       <c r="M299" s="53" t="inlineStr">
         <is>
-          <t>⑤ BOD/COD比は生物分解性の目安となる。</t>
+          <t>⑤ BOD−MLSS負荷 ── kg／(kg・日)</t>
         </is>
       </c>
     </row>
@@ -38422,7 +38424,7 @@
       </c>
       <c r="E300" s="52" t="inlineStr">
         <is>
-          <t>水質測定項目・測定方法</t>
+          <t>水質試験・BOD測定</t>
         </is>
       </c>
       <c r="F300" s="52" t="n">
@@ -38430,37 +38432,37 @@
       </c>
       <c r="G300" s="53" t="inlineStr">
         <is>
-          <t>水質汚濁防止・汚水処理技術および水質試験方法に関する正誤判定</t>
+          <t>排水のBOD測定方法（硝化抑制、20℃・5日間、希釈水栄養素、溶存酸素消費率、過飽和ばっ気）</t>
         </is>
       </c>
       <c r="H300" s="53" t="inlineStr">
         <is>
-          <t>水質分析に関する次の記述のうち，最も不適切なものはどれか。</t>
+          <t>排水の水質試験におけるBOD（生物化学的酸素要求量）の測定に関する次の記述のうち，最も不適切なものはどれか。</t>
         </is>
       </c>
       <c r="I300" s="53" t="inlineStr">
         <is>
-          <t>① BOD5 は 20℃ で 5 日間培養して測定する。</t>
+          <t>① 硝化作用を抑制した状態のBODの測定方法が定められている。</t>
         </is>
       </c>
       <c r="J300" s="53" t="inlineStr">
         <is>
-          <t>② DO 測定には電極法やウィンクラー法が用いられる。</t>
+          <t>② 試料を希釈水で希釈し，20℃で5日間放置したとき消費された溶存酸素量から求める。</t>
         </is>
       </c>
       <c r="K300" s="53" t="inlineStr">
         <is>
-          <t>③ 濁度は水の濁り具合を示す。</t>
+          <t>③ 希釈水には，好気性微生物の正常な発育に必要な微量の培養素（カルシウム，マグネシウム，鉄，窒素，りん等）を含有していること。</t>
         </is>
       </c>
       <c r="L300" s="53" t="inlineStr">
         <is>
-          <t>④ 大腸菌群数は，顕微鏡で全細胞数を目視で直数カウントするのみである。</t>
+          <t>④ 溶存酸素消費率が100%になるように試料を希釈する。</t>
         </is>
       </c>
       <c r="M300" s="53" t="inlineStr">
         <is>
-          <t>⑤ 吸光光度法は微量成分分析に汎用される。</t>
+          <t>⑤ 溶存酸素が過飽和の試料は，ばっ気などにより，溶存酸素を20℃の飽和量近くにする。</t>
         </is>
       </c>
     </row>
@@ -38487,7 +38489,7 @@
       </c>
       <c r="E301" s="52" t="inlineStr">
         <is>
-          <t>各種活性汚泥法(膜分離/嫌気好気等)</t>
+          <t>浄化槽の構造・処理方式</t>
         </is>
       </c>
       <c r="F301" s="52" t="n">
@@ -38495,37 +38497,37 @@
       </c>
       <c r="G301" s="53" t="inlineStr">
         <is>
-          <t>標準活性汚泥法、膜分離(MBR)、A2O法、ステップエアレーション等の特徴と運転条件の比較</t>
+          <t>浄化槽の構造基準に規定されている処理方式（標準活性汚泥方式）選定</t>
         </is>
       </c>
       <c r="H301" s="53" t="inlineStr">
         <is>
-          <t>生物処理に関する次の記述のうち，最も不適切なものはどれか。</t>
+          <t>浄化槽の構造基準（昭和55年建設省告示第1292号 最終改正平成18年国土交通省告示第154号に定める構造方法）に規定されている処理方式は，次のうちどれか。</t>
         </is>
       </c>
       <c r="I301" s="53" t="inlineStr">
         <is>
-          <t>① 標準活性汚泥法はばっ気槽と沈殿池で構成される。</t>
+          <t>① 担体流動方式</t>
         </is>
       </c>
       <c r="J301" s="53" t="inlineStr">
         <is>
-          <t>② A2O法は窒素とリンを同時に除去する。</t>
+          <t>② 膜分離活性汚泥方式</t>
         </is>
       </c>
       <c r="K301" s="53" t="inlineStr">
         <is>
-          <t>③ MBRは膜で固液分離を行う。</t>
+          <t>③ 回分式活性汚泥方式</t>
         </is>
       </c>
       <c r="L301" s="53" t="inlineStr">
         <is>
-          <t>④ 回転円板法は固定膜方式の一種である。</t>
+          <t>④ オキシデーションディッチ方式</t>
         </is>
       </c>
       <c r="M301" s="53" t="inlineStr">
         <is>
-          <t>⑤ 硝化反応は完全な嫌気性条件下でのみ進行する。</t>
+          <t>⑤ 標準活性汚泥方式</t>
         </is>
       </c>
     </row>
@@ -38552,7 +38554,7 @@
       </c>
       <c r="E302" s="52" t="inlineStr">
         <is>
-          <t>浄化槽の構造・処理方式</t>
+          <t>水質管理・消毒</t>
         </is>
       </c>
       <c r="F302" s="52" t="n">
@@ -38560,37 +38562,37 @@
       </c>
       <c r="G302" s="53" t="inlineStr">
         <is>
-          <t>浄化槽法および構造基準に基づく各種処理方式（単独・合併）、保守点検・清掃頻度の正誤判定</t>
+          <t>処理水の消毒（紫外線消毒、遊離塩素pH影響、塩素存在形態、オゾン残留性、オゾン消毒力）</t>
         </is>
       </c>
       <c r="H302" s="53" t="inlineStr">
         <is>
-          <t>浄化槽に関する次の記述のうち，最も不適切なものはどれか。</t>
+          <t>処理水の消毒に関する次の記述のうち，最も適切なものはどれか。</t>
         </is>
       </c>
       <c r="I302" s="53" t="inlineStr">
         <is>
-          <t>① 合併処理浄化槽はし尿と雑排水を処理する。</t>
+          <t>① 紫外線消毒は，浮遊物質が多い水に適している。</t>
         </is>
       </c>
       <c r="J302" s="53" t="inlineStr">
         <is>
-          <t>② 単独処理浄化槽は，環境負荷が小さいため今後の設置が推奨されている。</t>
+          <t>② 遊離塩素の消毒力は，pHの影響を顕著に受ける。</t>
         </is>
       </c>
       <c r="K302" s="53" t="inlineStr">
         <is>
-          <t>③ 法定検査の義務が定められている。</t>
+          <t>③ 塩素の消毒力は，塩素の存在形態にかかわらずほぼ一定である。</t>
         </is>
       </c>
       <c r="L302" s="53" t="inlineStr">
         <is>
-          <t>④ 保守点検や清掃が定期的に必要である。</t>
+          <t>④ オゾン消毒は，効果の残留性がある。</t>
         </is>
       </c>
       <c r="M302" s="53" t="inlineStr">
         <is>
-          <t>⑤ 消毒工程を経て放流される。</t>
+          <t>⑤ オゾンの消毒力は，塩素より弱い。</t>
         </is>
       </c>
     </row>
@@ -38617,7 +38619,7 @@
       </c>
       <c r="E303" s="52" t="inlineStr">
         <is>
-          <t>汚泥の含水率・濃縮計算</t>
+          <t>水質環境基準・適用水域</t>
         </is>
       </c>
       <c r="F303" s="52" t="n">
@@ -38625,37 +38627,37 @@
       </c>
       <c r="G303" s="53" t="inlineStr">
         <is>
-          <t>汚泥の含水率変化に伴う汚泥発生量・濃縮量の定型計算および沈降特性(SVI)に関する正誤判定</t>
+          <t>生活環境項目と適用水域の組合せ（BOD-湖沼、COD-海域、pH-河川、大腸菌群数-湖沼、DO-海域）</t>
         </is>
       </c>
       <c r="H303" s="53" t="inlineStr">
         <is>
-          <t>汚泥処理に関する次の記述のうち，最も不適切なものはどれか。</t>
+          <t>生活環境の保全に関する環境基準項目と適用される水域の組合せとして，最も不適切なものはどれか。</t>
         </is>
       </c>
       <c r="I303" s="53" t="inlineStr">
         <is>
-          <t>① 汚泥濃縮を行っても，汚泥の体積は全く変化しない。</t>
+          <t>① 生物化学的酸素要求量（BOD） ── 湖沼</t>
         </is>
       </c>
       <c r="J303" s="53" t="inlineStr">
         <is>
-          <t>② 嫌気性消化により発酵ガス（メタン）が得られる。</t>
+          <t>② 化学的酸素要求量（COD） ── 海域</t>
         </is>
       </c>
       <c r="K303" s="53" t="inlineStr">
         <is>
-          <t>③ 凝集剤の添加は脱水性を改善する。</t>
+          <t>③ 水素イオン濃度（pH） ── 河川</t>
         </is>
       </c>
       <c r="L303" s="53" t="inlineStr">
         <is>
-          <t>④ 焼却処理は減容化に効果的である。</t>
+          <t>④ 大腸菌群数 ── 湖沼</t>
         </is>
       </c>
       <c r="M303" s="53" t="inlineStr">
         <is>
-          <t>⑤ 遠心脱水機やベルトプレスが用いられる。</t>
+          <t>⑤ 溶存酸素量（DO） ── 海域</t>
         </is>
       </c>
     </row>
@@ -38682,7 +38684,7 @@
       </c>
       <c r="E304" s="52" t="inlineStr">
         <is>
-          <t>BOD/COD環境基準達成率</t>
+          <t>長時間ばっ気方式・計算</t>
         </is>
       </c>
       <c r="F304" s="52" t="n">
@@ -38690,37 +38692,38 @@
       </c>
       <c r="G304" s="53" t="inlineStr">
         <is>
-          <t>流入水量・BOD濃度・ばっ気槽容量に基づくBOD容積負荷およびHRT/BOD-MLSS負荷の定型計算</t>
+          <t>長時間ばっ気方式の計算・評価（流入BOD量24kg/日、HRT 16h、BOD容積負荷0.30kg/(m³・日)、返送率125%/150%、BOD除去率95%）</t>
         </is>
       </c>
       <c r="H304" s="53" t="inlineStr">
         <is>
-          <t>水質環境基準に関する次の記述のうち，最も不適切なものはどれか。</t>
+          <t>下図に示す長時間ばっ気方式の汚水処理施設に関する次の記述のうち，最も不適切なものはどれか。
+［条件・フロー図：流入120m³/日・BOD200mg/L、ばっ気槽80m³、返送汚泥150m³/日、放流120m³/日・BOD10mg/L］</t>
         </is>
       </c>
       <c r="I304" s="53" t="inlineStr">
         <is>
-          <t>① 河川には BOD 基準が設定されている。</t>
+          <t>① ばっ気槽の水力学的滞留時間（HRT）は，16時間である。</t>
         </is>
       </c>
       <c r="J304" s="53" t="inlineStr">
         <is>
-          <t>② 湖沼には COD 基準が設定されている。</t>
+          <t>② 施設への流入BOD量は，24kg／日である。</t>
         </is>
       </c>
       <c r="K304" s="53" t="inlineStr">
         <is>
-          <t>③ 富栄養化対策として窒素・リンの基準がある。</t>
+          <t>③ ばっ気槽のBOD容積負荷は，0.30kg／(m³・日)である。</t>
         </is>
       </c>
       <c r="L304" s="53" t="inlineStr">
         <is>
-          <t>④ 健康項目は，基準超過が日常的に全国で多発している。</t>
+          <t>④ ばっ気槽への汚泥返送率は，150%である。</t>
         </is>
       </c>
       <c r="M304" s="53" t="inlineStr">
         <is>
-          <t>⑤ 水生生物の保全に関する基準が設けられている。</t>
+          <t>⑤ 施設全体としてのBOD除去率は，95%である。</t>
         </is>
       </c>
     </row>
@@ -38742,12 +38745,12 @@
       </c>
       <c r="D305" s="52" t="inlineStr">
         <is>
-          <t>水質管理</t>
+          <t>廃棄物管理</t>
         </is>
       </c>
       <c r="E305" s="52" t="inlineStr">
         <is>
-          <t>水質汚濁防止法排水基準</t>
+          <t>リサイクル関連法・公布順</t>
         </is>
       </c>
       <c r="F305" s="52" t="n">
@@ -38755,37 +38758,42 @@
       </c>
       <c r="G305" s="53" t="inlineStr">
         <is>
-          <t>水質汚濁防止・汚水処理技術および水質試験方法に関する正誤判定</t>
+          <t>昭和以降の廃棄物・リサイクル関連法の公布年月日順並べ替え（廃掃法→再生資源利用促進法→特定有害廃棄物輸出入規制法→容器包装リサイクル法→循環型社会基本法）</t>
         </is>
       </c>
       <c r="H305" s="53" t="inlineStr">
         <is>
-          <t>水質汚濁防止法に関する次の記述のうち，最も不適切なものはどれか。</t>
+          <t>我が国の昭和以降の廃棄物・リサイクル関連法制度について，次の（ア）〜（オ）の法律の公布年月日が古いものから順に並べられたものはどれか。
+（ア）循環型社会形成推進基本法
+（イ）廃棄物の処理及び清掃に関する法律
+（ウ）再生資源の利用の促進に関する法律
+（エ）特定有害廃棄物等の輸出入等の規制に関する法律
+（オ）容器包装に係る分別収集及び再商品化の促進等に関する法律</t>
         </is>
       </c>
       <c r="I305" s="53" t="inlineStr">
         <is>
-          <t>① 特定施設からの排出水に規制が適用される。</t>
+          <t>① ア → イ → オ → ウ → エ</t>
         </is>
       </c>
       <c r="J305" s="53" t="inlineStr">
         <is>
-          <t>② 都道府県は上乗せ基準を設定できる。</t>
+          <t>② ア → イ → エ → オ → ウ</t>
         </is>
       </c>
       <c r="K305" s="53" t="inlineStr">
         <is>
-          <t>③ 有害物質の地下浸透規制がある。</t>
+          <t>③ イ → ウ → エ → ア → オ</t>
         </is>
       </c>
       <c r="L305" s="53" t="inlineStr">
         <is>
-          <t>④ 事故時の措置や届出義務は完全免除されている。</t>
+          <t>④ イ → ウ → エ → オ → ア</t>
         </is>
       </c>
       <c r="M305" s="53" t="inlineStr">
         <is>
-          <t>⑤ 指定水域での総量規制が適用される。</t>
+          <t>⑤ イ → オ → ア → ウ → エ</t>
         </is>
       </c>
     </row>
@@ -38807,12 +38815,12 @@
       </c>
       <c r="D306" s="52" t="inlineStr">
         <is>
-          <t>水質管理</t>
+          <t>廃棄物管理</t>
         </is>
       </c>
       <c r="E306" s="52" t="inlineStr">
         <is>
-          <t>消毒(塩素/オゾン/紫外線)</t>
+          <t>ごみ排出・統計数値</t>
         </is>
       </c>
       <c r="F306" s="52" t="n">
@@ -38820,37 +38828,38 @@
       </c>
       <c r="G306" s="53" t="inlineStr">
         <is>
-          <t>遊離残留塩素、結合残留塩素（クロラミン）、オゾン、紫外線消毒の殺菌力・残留性比較</t>
+          <t>平成29年度の1人1日当たりごみ排出量（920g）と平成24年度対比（44g減少）の穴埋め</t>
         </is>
       </c>
       <c r="H306" s="53" t="inlineStr">
         <is>
-          <t>水処理における消毒技術に関する次の記述のうち，最も不適切なものはどれか。</t>
+          <t>我が国の廃棄物の発生量に関する次の記述の，［　］に入る数量の組合せとして最も適切なものはどれか。
+「一般廃棄物の排出及び処理状況等（平成29年度）について」によると，平成29年度における1人1日当たりのごみ排出量は［ ア ］グラムである。平成24年度と比べると，［ イ ］グラム［ ウ ］している。</t>
         </is>
       </c>
       <c r="I306" s="53" t="inlineStr">
         <is>
-          <t>① 塩素消毒は，残留効果（残留塩素）をもつ利点がある。</t>
+          <t>① 1,033 ／ 260 ／ 増加</t>
         </is>
       </c>
       <c r="J306" s="53" t="inlineStr">
         <is>
-          <t>② 結合残留塩素（クロラミン）は，遊離残留塩素に比べて殺菌力が遅いが持続性がある。</t>
+          <t>② 1,033 ／ 260 ／ 減少</t>
         </is>
       </c>
       <c r="K306" s="53" t="inlineStr">
         <is>
-          <t>③ 紫外線（UV）消毒は，強い残留効果が長時間維持されるため，配管網の末端消毒に最適である。</t>
+          <t>③ 920 ／ 44 ／ 減少</t>
         </is>
       </c>
       <c r="L306" s="53" t="inlineStr">
         <is>
-          <t>④ オゾン消毒は，強力な酸化力をもつが，水中の残留性が低いため末端補強が必要となる。</t>
+          <t>④ 920 ／ 44 ／ 増加</t>
         </is>
       </c>
       <c r="M306" s="53" t="inlineStr">
         <is>
-          <t>⑤ トリハロメタン（THM）は，塩素と水中の有機物が反応して生じる副生成物である。</t>
+          <t>⑤ 1,033 ／ 44 ／ 減少</t>
         </is>
       </c>
     </row>
@@ -38872,12 +38881,12 @@
       </c>
       <c r="D307" s="52" t="inlineStr">
         <is>
-          <t>水質管理</t>
+          <t>廃棄物管理</t>
         </is>
       </c>
       <c r="E307" s="52" t="inlineStr">
         <is>
-          <t>硝化・脱窒反応</t>
+          <t>廃棄物処理法・基本原則</t>
         </is>
       </c>
       <c r="F307" s="52" t="n">
@@ -38885,37 +38894,37 @@
       </c>
       <c r="G307" s="53" t="inlineStr">
         <is>
-          <t>水質汚濁防止・汚水処理技術および水質試験方法に関する正誤判定</t>
+          <t>廃棄物処理法（目的、市町村の一般廃棄物計画・収集処分、排出事業者責任、処理委託、特別管理産業廃棄物定義）</t>
         </is>
       </c>
       <c r="H307" s="53" t="inlineStr">
         <is>
-          <t>窒素除去反応に関する次の記述のうち，最も不適切なものはどれか。</t>
+          <t>廃棄物の処理及び清掃に関する法律（廃棄物処理法）に関する次の記述のうち，最も不適切なものはどれか。</t>
         </is>
       </c>
       <c r="I307" s="53" t="inlineStr">
         <is>
-          <t>① 硝化反応は，無酸素条件下で進行する還元反応である。</t>
+          <t>① 法律の目的は，汚物を衛生的に処理し，生活環境を清潔にすることにより，公衆衛生の向上を図ることである。</t>
         </is>
       </c>
       <c r="J307" s="53" t="inlineStr">
         <is>
-          <t>② 硝化菌（亜硝酸菌・硝酸菌）は好気性独立栄養細菌である。</t>
+          <t>② 市町村は，一般廃棄物の処理計画を定め，その区域内の一般廃棄物を収集，処理処分しなければならない。</t>
         </is>
       </c>
       <c r="K307" s="53" t="inlineStr">
         <is>
-          <t>③ 脱窒反応は，無酸素条件（通気なし）で脱窒菌により進行する。</t>
+          <t>③ 産業廃棄物の処理は，汚染者負担の原則に基づいて排出事業者自身に処理責任がある。</t>
         </is>
       </c>
       <c r="L307" s="53" t="inlineStr">
         <is>
-          <t>④ 脱窒反応では有機物（炭素源）が消費される。</t>
+          <t>④ 産業廃棄物の処理は，都道府県知事の許可を得た処理業者に委託することができる。</t>
         </is>
       </c>
       <c r="M307" s="53" t="inlineStr">
         <is>
-          <t>⑤ 脱窒により窒素ガス（N2）として気体放出される。</t>
+          <t>⑤ 特別管理産業廃棄物とは，産業廃棄物のうち，爆発性，毒性，感染性その他の人の健康又は生活環境に係る被害を生ずるおそれがある性状を有するものとして政令で定めるものをいう。</t>
         </is>
       </c>
     </row>
@@ -38937,12 +38946,12 @@
       </c>
       <c r="D308" s="52" t="inlineStr">
         <is>
-          <t>水質管理</t>
+          <t>廃棄物管理</t>
         </is>
       </c>
       <c r="E308" s="52" t="inlineStr">
         <is>
-          <t>DO測定法・大腸菌数測定</t>
+          <t>有害廃棄物・PCB</t>
         </is>
       </c>
       <c r="F308" s="52" t="n">
@@ -38950,37 +38959,37 @@
       </c>
       <c r="G308" s="53" t="inlineStr">
         <is>
-          <t>水質汚濁防止・汚水処理技術および水質試験方法に関する正誤判定</t>
+          <t>PCB（ポリ塩化ビフェニル）の性質、異性体、水溶性・安定性、用途、カネミ油症事件</t>
         </is>
       </c>
       <c r="H308" s="53" t="inlineStr">
         <is>
-          <t>水質測定手法に関する次の記述のうち，最も不適切なものはどれか。</t>
+          <t>PCB（ポリ塩化ビフェニル）に関する次の記述のうち，最も不適切なものはどれか。</t>
         </is>
       </c>
       <c r="I308" s="53" t="inlineStr">
         <is>
-          <t>① ウィンクラー法は，溶存酸素（DO）の滴定測定法である。</t>
+          <t>① PCBの構造は，塩素の位置と数によって多くの異性体がある。</t>
         </is>
       </c>
       <c r="J308" s="53" t="inlineStr">
         <is>
-          <t>② DOメーター（電極法）は，測定に数日間の培養時間を要する。</t>
+          <t>② 化学的に安定で，酸・アルカリに侵されず，水によく溶ける。</t>
         </is>
       </c>
       <c r="K308" s="53" t="inlineStr">
         <is>
-          <t>③ 最確数法（MPN法）は大腸菌群数の測定に用いられる。</t>
+          <t>③ PCBは，変圧器や熱交換器で使用するための安定した熱媒体として開発された。</t>
         </is>
       </c>
       <c r="L308" s="53" t="inlineStr">
         <is>
-          <t>④ 検知管法はガスの簡易測定に適している。</t>
+          <t>④ 不燃性で加熱・冷却しても性質が変わらない。</t>
         </is>
       </c>
       <c r="M308" s="53" t="inlineStr">
         <is>
-          <t>⑤ フレーム原子吸光法は金属元素分析に用いられる。</t>
+          <t>⑤ 福岡県で米ぬか油にPCBが漏れて混入し，カネミ油症事件が起きた。</t>
         </is>
       </c>
     </row>
@@ -39002,12 +39011,12 @@
       </c>
       <c r="D309" s="52" t="inlineStr">
         <is>
-          <t>水質管理</t>
+          <t>廃棄物管理</t>
         </is>
       </c>
       <c r="E309" s="52" t="inlineStr">
         <is>
-          <t>BOD測定・BOD容積負荷計算</t>
+          <t>ダイオキシン類対策・焼却温度</t>
         </is>
       </c>
       <c r="F309" s="52" t="n">
@@ -39015,37 +39024,37 @@
       </c>
       <c r="G309" s="53" t="inlineStr">
         <is>
-          <t>流入水量・BOD濃度・ばっ気槽容量に基づくBOD容積負荷およびHRT/BOD-MLSS負荷の定型計算</t>
+          <t>廃棄物焼却温度（燃焼室内温度800〜900℃、ダイオキシン抑熱800℃以上、溶融950℃超、悪臭分解700℃以上、Thermal NOx 1000〜1300℃超）</t>
         </is>
       </c>
       <c r="H309" s="53" t="inlineStr">
         <is>
-          <t>下水処理場の管理指標に関する次の記述のうち，最も不適切なものはどれか。</t>
+          <t>廃棄物の焼却温度に関する次の記述のうち，最も不適切なものはどれか。</t>
         </is>
       </c>
       <c r="I309" s="53" t="inlineStr">
         <is>
-          <t>① BOD容積負荷は，ばっ気槽単位容積当たりの日BOD流入量である。</t>
+          <t>① 廃棄物焼却炉における燃焼室内温度は，通常800〜900℃程度に保たれている。</t>
         </is>
       </c>
       <c r="J309" s="53" t="inlineStr">
         <is>
-          <t>② BOD-SS負荷は，活性汚泥量に対するBOD負荷量を示す。</t>
+          <t>② ダイオキシン類の生成を抑えるには，800℃以上が必要とされる。</t>
         </is>
       </c>
       <c r="K309" s="53" t="inlineStr">
         <is>
-          <t>③ 水力学的滞留時間（HRT）は，槽容積を流入水量で除した値である。</t>
+          <t>③ 950℃を超えると焼却灰の溶融が起こり，炉壁や冷却装置などに付着する可能性がある。</t>
         </is>
       </c>
       <c r="L309" s="53" t="inlineStr">
         <is>
-          <t>④ SVI は，汚泥の沈降濃縮性を示す指標である。</t>
+          <t>④ 悪臭物質（アンモニアやメチルメルカプタンなど）や有害物質（ホルムアルデヒドやシアン化水素など）の分解には，700℃以上が必要とされる。</t>
         </is>
       </c>
       <c r="M309" s="53" t="inlineStr">
         <is>
-          <t>⑤ SVI が 200 以上と高くなると，汚泥沈降性が極めて良好になる。</t>
+          <t>⑤ 750℃以下になると空気中の窒素と酸素が反応して，いわゆるThermal NOxが発生する。</t>
         </is>
       </c>
     </row>
@@ -39067,12 +39076,12 @@
       </c>
       <c r="D310" s="52" t="inlineStr">
         <is>
-          <t>水質管理</t>
+          <t>廃棄物管理</t>
         </is>
       </c>
       <c r="E310" s="52" t="inlineStr">
         <is>
-          <t>水質測定項目・測定方法</t>
+          <t>廃棄物選別技術</t>
         </is>
       </c>
       <c r="F310" s="52" t="n">
@@ -39080,37 +39089,37 @@
       </c>
       <c r="G310" s="53" t="inlineStr">
         <is>
-          <t>水質汚濁防止・汚水処理技術および水質試験方法に関する正誤判定</t>
+          <t>廃棄物の選別技術（ふるい選別・トロンメル、渦電流選別・導電性金属選別、磁力選別、手選別、比重選別）</t>
         </is>
       </c>
       <c r="H310" s="53" t="inlineStr">
         <is>
-          <t>下水管渠及び処理施設に関する次の記述のうち，最も不適切なものはどれか。</t>
+          <t>廃棄物の選別技術に関する次の記述のうち，最も適切なものはどれか。</t>
         </is>
       </c>
       <c r="I310" s="53" t="inlineStr">
         <is>
-          <t>① 分流式下水道は，汚水と雨水を別々の管渠で排除する。</t>
+          <t>① ふるい選別には，トロンメルや振動ふるいなどの方式があるが，いずれも選別精度が高く効果的な選別ができる。</t>
         </is>
       </c>
       <c r="J310" s="53" t="inlineStr">
         <is>
-          <t>② 合流式下水道は，雨水時に未処理汚水が排出されるリスクが一切存在しない完璧なシステムである。</t>
+          <t>② 渦電流選別は，鉄が除かれた混合ごみから，非鉄金属とプラスチック等の電流を通さない（非導電性）物質を選別する技術である。</t>
         </is>
       </c>
       <c r="K310" s="53" t="inlineStr">
         <is>
-          <t>③ 下水管渠内の流速は，固形物の沈殿防止と摩耗防止の観点から適切な範囲に保つ。</t>
+          <t>③ 磁力選別は選別精度が高いため，金属類と有機系のごみとの混合ごみからでもダスト等の混入のない高純度の資源を得られるので，それらをあらかじめ分別等をしておくことはない。</t>
         </is>
       </c>
       <c r="L310" s="53" t="inlineStr">
         <is>
-          <t>④ 最初の沈殿池は，重力沈降によりSSを除去する。</t>
+          <t>④ 手選別による廃棄物の選別は，コスト，効率の点で不利なので，今日の我が国の廃棄物処理では，ほとんど行われていない。</t>
         </is>
       </c>
       <c r="M310" s="53" t="inlineStr">
         <is>
-          <t>⑤ 最終沈殿池は，活性汚泥を固液分離して上澄水を得る。</t>
+          <t>⑤ 比重選別はごみの比重の違いで選別する方法であり，廃棄物処理では液体中での比重差で分離する方法が一般的である。</t>
         </is>
       </c>
     </row>
@@ -39132,12 +39141,12 @@
       </c>
       <c r="D311" s="52" t="inlineStr">
         <is>
-          <t>水質管理</t>
+          <t>廃棄物管理</t>
         </is>
       </c>
       <c r="E311" s="52" t="inlineStr">
         <is>
-          <t>各種活性汚泥法(膜分離/嫌気好気等)</t>
+          <t>ごみ処理・統計数値</t>
         </is>
       </c>
       <c r="F311" s="52" t="n">
@@ -39145,37 +39154,38 @@
       </c>
       <c r="G311" s="53" t="inlineStr">
         <is>
-          <t>標準活性汚泥法、膜分離(MBR)、A2O法、ステップエアレーション等の特徴と運転条件の比較</t>
+          <t>2017年度の一般廃棄物処理における中間処理率（94%）、総資源化率（20%）、最終処分率（3%）の数値選定</t>
         </is>
       </c>
       <c r="H311" s="53" t="inlineStr">
         <is>
-          <t>高度処理技術に関する次の記述のうち，最も不適切なものはどれか。</t>
+          <t>一般廃棄物に関する次の記述の，［　］に入る数値の組合せとして，最も適切なものはどれか。
+2017年度の一般廃棄物の処理において，総処理量に対する中間処理量の割合は，［ A ］%である。また，総資源化量（中間処理後の再生利用を含めた量）と最終処分量の割合は総排出量に対し，それぞれ［ B ］%，［ C ］%である。</t>
         </is>
       </c>
       <c r="I311" s="53" t="inlineStr">
         <is>
-          <t>① 凝集加圧浮上法は，微細気泡で浮遊物を浮上分離する。</t>
+          <t>① 84 ／ 20 ／ 5</t>
         </is>
       </c>
       <c r="J311" s="53" t="inlineStr">
         <is>
-          <t>② 活性炭吸着は，微量有機物や色度・臭気の除去に有効である。</t>
+          <t>② 84 ／ 30 ／ 3</t>
         </is>
       </c>
       <c r="K311" s="53" t="inlineStr">
         <is>
-          <t>③ 逆浸透（RO）膜は，懸濁粒子のみを通し純水分子を完全に阻止する。</t>
+          <t>③ 94 ／ 20 ／ 9</t>
         </is>
       </c>
       <c r="L311" s="53" t="inlineStr">
         <is>
-          <t>④ オゾン処理は，脱色・脱臭・除菌効果をもつ。</t>
+          <t>④ 94 ／ 30 ／ 5</t>
         </is>
       </c>
       <c r="M311" s="53" t="inlineStr">
         <is>
-          <t>⑤ 膜濾過処理（MF/UF）は，処理水の再利用に寄与する。</t>
+          <t>⑤ 94 ／ 20 ／ 3</t>
         </is>
       </c>
     </row>
@@ -39197,12 +39207,12 @@
       </c>
       <c r="D312" s="52" t="inlineStr">
         <is>
-          <t>水質管理</t>
+          <t>廃棄物管理</t>
         </is>
       </c>
       <c r="E312" s="52" t="inlineStr">
         <is>
-          <t>浄化槽の構造・処理方式</t>
+          <t>最終処分場の構造・維持管理</t>
         </is>
       </c>
       <c r="F312" s="52" t="n">
@@ -39210,37 +39220,37 @@
       </c>
       <c r="G312" s="53" t="inlineStr">
         <is>
-          <t>浄化槽法および構造基準に基づく各種処理方式（単独・合併）、保守点検・清掃頻度の正誤判定</t>
+          <t>一般廃棄物・産業廃棄物管理型最終処分場の構造（準好気性埋立構造、浸出水集排水施設、遮水工・二重遮水工等、浸出水調整池、被覆型処分場）</t>
         </is>
       </c>
       <c r="H312" s="53" t="inlineStr">
         <is>
-          <t>浄化槽の維持管理に関する次の記述のうち，最も不適切なものはどれか。</t>
+          <t>一般廃棄物最終処分場及び産業廃棄物管理型最終処分場の主な施設に関する次の記述のうち，最も不適切なものはどれか。</t>
         </is>
       </c>
       <c r="I312" s="53" t="inlineStr">
         <is>
-          <t>① 保守点検は，機器調整や消毒剤補給などを行う。</t>
+          <t>① 日本においては，自然換気により好気性領域を拡大させる準好気性埋立構造の埋立地形式が主流である。</t>
         </is>
       </c>
       <c r="J312" s="53" t="inlineStr">
         <is>
-          <t>② 清掃は，汚泥の引き抜きや調整等を行う。</t>
+          <t>② 浸出水集排水施設とは，浸出水を速やかに集水し排水する機能と埋立地内の好気性ゾーンを拡大する機能を持つものである。</t>
         </is>
       </c>
       <c r="K312" s="53" t="inlineStr">
         <is>
-          <t>③ 法定検査は，浄化槽清掃業者が自ら合否判定を行う自社検査である。</t>
+          <t>③ 遮水工は，地下水汚染防止の目的で設置されるものであり，表面遮水工のみの設置が義務付けられている。</t>
         </is>
       </c>
       <c r="L312" s="53" t="inlineStr">
         <is>
-          <t>④ 処理水の放流基準が定められている。</t>
+          <t>④ 浸出水処理施設は，基本的に一定の処理量を前提に設計，運転されるため，浸出水量の変動を吸収するための浸出水調整池が設けられる。</t>
         </is>
       </c>
       <c r="M312" s="53" t="inlineStr">
         <is>
-          <t>⑤ 浄化槽技術管理者の設置が必要な規模がある。</t>
+          <t>⑤ 被覆型最終処分場とは，埋立地に屋根をかけたものであり，降雨が埋立地に入ることを制御できるため，浸出水処理の負担は軽い。</t>
         </is>
       </c>
     </row>
@@ -39262,12 +39272,12 @@
       </c>
       <c r="D313" s="52" t="inlineStr">
         <is>
-          <t>水質管理</t>
+          <t>廃棄物管理</t>
         </is>
       </c>
       <c r="E313" s="52" t="inlineStr">
         <is>
-          <t>汚泥の含水率・濃縮計算</t>
+          <t>最終処分場・浸出水量計算</t>
         </is>
       </c>
       <c r="F313" s="52" t="n">
@@ -39275,37 +39285,38 @@
       </c>
       <c r="G313" s="53" t="inlineStr">
         <is>
-          <t>汚泥の含水率変化に伴う汚泥発生量・濃縮量の定型計算および沈降特性(SVI)に関する正誤判定</t>
+          <t>オープン型最終処分場の日平均浸出水発生量（70m³/日）と浸出係数（0.6）の計算（面積2.5ha、降水量1700mm/年、蒸発散量2.0mm/日）</t>
         </is>
       </c>
       <c r="H313" s="53" t="inlineStr">
         <is>
-          <t>汚泥の脱水・焼却に関する次の記述のうち，最も不適切なものはどれか。</t>
+          <t>最終処分場の浸出水量に関する次の記述の，［　］に入る数値の組合せとして，最も適切なものはどれか。
+表面遮水工が設置されているオープン型最終処分場において，埋立面積が2.5ha，年間降水量が1700mm／年，蒸発散量が2.0mm／日の場合，日平均浸出水発生量は［ A ］m³／日，浸出係数は［ B ］である。ただし，埋立地に降った雨水が表流水として外部へ排除されることはないものとする。</t>
         </is>
       </c>
       <c r="I313" s="53" t="inlineStr">
         <is>
-          <t>① 濃縮汚泥に凝集剤を添加してフロックを形成させる。</t>
+          <t>① 50 ／ 0.4</t>
         </is>
       </c>
       <c r="J313" s="53" t="inlineStr">
         <is>
-          <t>② 脱水ケーキの含水率は 75〜85% 程度となる。</t>
+          <t>② 50 ／ 0.6</t>
         </is>
       </c>
       <c r="K313" s="53" t="inlineStr">
         <is>
-          <t>③ 焼却により汚泥中の有機物は分解焼失する。</t>
+          <t>③ 70 ／ 0.4</t>
         </is>
       </c>
       <c r="L313" s="53" t="inlineStr">
         <is>
-          <t>④ 焼却灰は，すべて無条件に海洋投棄される。</t>
+          <t>④ 70 ／ 0.6</t>
         </is>
       </c>
       <c r="M313" s="53" t="inlineStr">
         <is>
-          <t>⑤ 脱水機の選定は汚泥性状に応じて行われる。</t>
+          <t>⑤ 90 ／ 0.8</t>
         </is>
       </c>
     </row>
@@ -39327,12 +39338,12 @@
       </c>
       <c r="D314" s="52" t="inlineStr">
         <is>
-          <t>水質管理</t>
+          <t>廃棄物管理</t>
         </is>
       </c>
       <c r="E314" s="52" t="inlineStr">
         <is>
-          <t>BOD/COD環境基準達成率</t>
+          <t>環境影響評価・生活環境影響調査</t>
         </is>
       </c>
       <c r="F314" s="52" t="n">
@@ -39340,37 +39351,37 @@
       </c>
       <c r="G314" s="53" t="inlineStr">
         <is>
-          <t>流入水量・BOD濃度・ばっ気槽容量に基づくBOD容積負荷およびHRT/BOD-MLSS負荷の定型計算</t>
+          <t>廃棄物処理施設生活環境影響調査指針（義務付け施設、変更許可時も必要、動植物調査含まない、調査事項、縦覧・意見聴取手続）</t>
         </is>
       </c>
       <c r="H314" s="53" t="inlineStr">
         <is>
-          <t>水質汚濁防止対策に関する次の記述のうち，最も不適切なものはどれか。</t>
+          <t>「廃棄物処理施設生活環境影響調査指針（平成18年9月環境省）」に関する次の記述のうち，最も不適切なものはどれか。</t>
         </is>
       </c>
       <c r="I314" s="53" t="inlineStr">
         <is>
-          <t>① 総量削減基本方針に基づき，指定水域の負荷削減が進められる。</t>
+          <t>① 生活環境影響調査は，許可を要するすべての廃棄物処理施設について実施が義務づけられている。</t>
         </is>
       </c>
       <c r="J314" s="53" t="inlineStr">
         <is>
-          <t>② 面源汚染（生活雑排水や農地雨水等）は，一点から集中排出されるため捕捉が非常に容易である。</t>
+          <t>② 生活環境影響調査は，廃棄物処理施設の変更の許可を受ける場合は不要である。</t>
         </is>
       </c>
       <c r="K314" s="53" t="inlineStr">
         <is>
-          <t>③ 閉鎖性水域では，富栄養化による赤潮や青潮の発生が問題となる。</t>
+          <t>③ 動物・植物調査は生活環境影響調査の対象とする調査事項には含まれていない。</t>
         </is>
       </c>
       <c r="L314" s="53" t="inlineStr">
         <is>
-          <t>④ 下水道の整備は，水質改善に大きく貢献している。</t>
+          <t>④ 調査事項は，廃棄物処理施設の稼働並びに当該施設に係る廃棄物の搬出入及び保管に伴って生じる生活環境への影響に関するものである。</t>
         </is>
       </c>
       <c r="M314" s="53" t="inlineStr">
         <is>
-          <t>⑤ 底質浄化や浚渫事業も水環境改善に有効である。</t>
+          <t>⑤ 廃棄物処理施設のうち，焼却施設及び最終処分場については，知事により申請書及び生活環境影響調査書が縦覧され，住民，市町村長の意見聴取，専門家の意見聴取等の手続が行われる。</t>
         </is>
       </c>
     </row>
@@ -39392,12 +39403,12 @@
       </c>
       <c r="D315" s="52" t="inlineStr">
         <is>
-          <t>水質管理</t>
+          <t>廃棄物管理</t>
         </is>
       </c>
       <c r="E315" s="52" t="inlineStr">
         <is>
-          <t>水質汚濁防止法排水基準</t>
+          <t>災害廃棄物対策</t>
         </is>
       </c>
       <c r="F315" s="52" t="n">
@@ -39405,37 +39416,37 @@
       </c>
       <c r="G315" s="53" t="inlineStr">
         <is>
-          <t>水質汚濁防止・汚水処理技術および水質試験方法に関する正誤判定</t>
+          <t>大規模災害発生時における災害廃棄物対策行動指針（基本的考え方、市町村の固有事務、一次仮置場撤去、後工程・分別考慮、コンクリートくず早期処理）</t>
         </is>
       </c>
       <c r="H315" s="53" t="inlineStr">
         <is>
-          <t>工場排水処理に関する次の記述のうち，最も不適切なものはどれか。</t>
+          <t>「大規模災害発生時における災害廃棄物対策行動指針（平成27年11月 環境省大臣官房廃棄物・リサイクル対策部）」に関する次の記述のうち，最も不適切なものはどれか。</t>
         </is>
       </c>
       <c r="I315" s="53" t="inlineStr">
         <is>
-          <t>① 中和処理は，酸・アルカリ排水のpHを調整する。</t>
+          <t>① この指針は，大規模災害発生時においても災害廃棄物を適正かつ円滑・迅速に処理するための基本的考え方，対応方針を整理するものである。</t>
         </is>
       </c>
       <c r="J315" s="53" t="inlineStr">
         <is>
-          <t>② 凝集沈殿法は，重金属やSSの除去に用いられる。</t>
+          <t>② 災害廃棄物の処理は市町村が行う固有事務として位置付けられている。</t>
         </is>
       </c>
       <c r="K315" s="53" t="inlineStr">
         <is>
-          <t>③ シアン化合物は，高濃度塩素等で分解処理される。</t>
+          <t>③ 大規模災害発生時に道路際や空地等に集積された廃棄物は，可能な限り分別した上で速やかに一次仮置場へ運搬，撤去する。</t>
         </is>
       </c>
       <c r="L315" s="53" t="inlineStr">
         <is>
-          <t>④ 六価クロムは，還元処理して三価クロムにして沈殿させる。</t>
+          <t>④ 災害廃棄物の選別に当たっては，後工程となる焼却処理や再生利用を効率的に行う観点から処理方針を検討する。</t>
         </is>
       </c>
       <c r="M315" s="53" t="inlineStr">
         <is>
-          <t>⑤ 油分含有排水は，処理なしでそのまま河川へ放流してよい。</t>
+          <t>⑤ 災害廃棄物の処理期間は，地域及び災害廃棄物の特性に応じて柔軟に設定すべきものであるが，特にコンクリートくずは早期に処理すべきものである。</t>
         </is>
       </c>
     </row>
@@ -39457,12 +39468,12 @@
       </c>
       <c r="D316" s="52" t="inlineStr">
         <is>
-          <t>水質管理</t>
+          <t>廃棄物管理</t>
         </is>
       </c>
       <c r="E316" s="52" t="inlineStr">
         <is>
-          <t>消毒(塩素/オゾン/紫外線)</t>
+          <t>指定廃棄物・放射性物質</t>
         </is>
       </c>
       <c r="F316" s="52" t="n">
@@ -39470,37 +39481,38 @@
       </c>
       <c r="G316" s="53" t="inlineStr">
         <is>
-          <t>遊離残留塩素、結合残留塩素（クロラミン）、オゾン、紫外線消毒の殺菌力・残留性比較</t>
+          <t>指定廃棄物の定義基準（8,000Bq/kg）と福島県内除染土壌・指定廃棄物等の中間貯蔵施設保管基準（10万Bq/kg）の穴埋め</t>
         </is>
       </c>
       <c r="H316" s="53" t="inlineStr">
         <is>
-          <t>水環境保全と持続可能社会に関する次の記述のうち，最も不適切なものはどれか。</t>
+          <t>指定廃棄物に関する次の記述の，［　］に入る数値の組合せとして，最も適切なものはどれか。
+2011年3月に発生した原子力発電所の事故で放射性物質により汚染された廃棄物のうち，［ A ］ベクレル／kgを超えるものを指定廃棄物とし，国の責任のもと，適切な方法で処理することとなっている。また，福島県内で除染に伴い発生した除染土壌や［ B ］ベクレル／kgを超える指定廃棄物等を安全に集中的に管理・保管するために中間貯蔵施設の整備が進められている。</t>
         </is>
       </c>
       <c r="I316" s="53" t="inlineStr">
         <is>
-          <t>① 水循環基本法に基づき，健全な水循環の維持が目指されている。</t>
+          <t>① 100 ／ 8,000</t>
         </is>
       </c>
       <c r="J316" s="53" t="inlineStr">
         <is>
-          <t>② 処理水の再利用は，節水及び資源循環に寄与する。</t>
+          <t>② 100 ／ 5万</t>
         </is>
       </c>
       <c r="K316" s="53" t="inlineStr">
         <is>
-          <t>③ 雨水の有効利用（中水道等）が進められている。</t>
+          <t>③ 1,000 ／ 10万</t>
         </is>
       </c>
       <c r="L316" s="53" t="inlineStr">
         <is>
-          <t>④ 下水汚泥のエネルギー利用（メタン発酵・燃料化）が期待されている。</t>
+          <t>④ 8,000 ／ 5万</t>
         </is>
       </c>
       <c r="M316" s="53" t="inlineStr">
         <is>
-          <t>⑤ 水処理プロセスでの電力消費や温室効果ガス排出は地球温暖化と無関係である。</t>
+          <t>⑤ 8,000 ／ 10万</t>
         </is>
       </c>
     </row>
@@ -71471,2102 +71483,2114 @@
       </c>
     </row>
     <row r="2" ht="65" customHeight="1">
-      <c r="A2" s="46" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>R1本-01</t>
         </is>
       </c>
-      <c r="B2" s="46" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Ⅲ-1</t>
         </is>
       </c>
-      <c r="C2" s="46" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>建築環境・設備・建築物衛生管理</t>
         </is>
       </c>
-      <c r="D2" s="46" t="inlineStr">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>照度・光環境</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>点光源からの水平面照度計算</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>下図に示す点光源に照らされたＡ点の水平面照度に最も近い値はどれか。ただし，点光源の配光特性は一様なものとし，反射は考慮しないものとする。
+［条件：点光源（光度200cd）、高さ2m、照射角60°、A点］</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>① 6.3 lx</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>② 8.3 lx</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>③ 10.8 lx</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>④ 12.5 lx</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>⑤ 50.0 lx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="65" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>R1本-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ⅲ-2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>建築環境・設備・建築物衛生管理</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>温熱環境・室内温度分布</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>室内の上下温度分布、日射・隙間風影響、上昇気流、居住域空調およびエアフローウィンドウ</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>室内の温度分布に関する次の記述のうち，最も不適切なものはどれか。</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>① 良好な温熱環境を実現するためには，極端な室内温度分布が生じるのは好ましくないため，床上0.1mから1.1m間の上下温度分布は5℃以内に抑えるのが好ましい。</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>② 夏期に日射熱が室内へ侵入する場合や外気温が高い場合は，窓側の空気温度は室の奥よりも高くなり，冬期に隙間風が侵入する場合や外気温が低い場合は，窓側の空気温度は低くなる傾向にある。</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>③ 室内には種々の発熱体が存在し，近傍の空気温度を上昇させる。この高温空気は密度が小さいため，浮力により上昇気流が発生する場合がある。</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>④ 空調・換気設備は，床面より1.8m程度までの居住域を良好な温熱空気環境に保つことが目的であるが，室内に温度分布を生じさせる原因でもある。</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>⑤ エアフローウィンドウは，2枚のガラスの間にブラインドを設けたもので，窓枠下部から室内空気を吸引し，これを窓上部から排気するものである。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="65" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>R1本-03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ⅲ-3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>建築環境・設備・建築物衛生管理</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>伝熱・熱伝導・熱移動</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>材料の熱定数（中空層熱抵抗、グラスウール・畳・ALC・二重ガラスの熱伝導率・熱抵抗）</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>材料の熱定数に関する次の記述のうち，最も不適切なものはどれか。</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>① 中空層の熱抵抗は，熱流方向が下向きの方が上向きより大きい。</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>② グラスウールの熱伝導率は，かさ比重が小さいほど小さくなる傾向がある。</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>③ 畳の熱伝導率は，木材と同程度である。</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>④ ALCの熱伝導率は，普通コンクリートの1／10程度である。</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>⑤ 二重ガラスなど密閉中空層の熱抵抗は，壁の中空層など半密閉中空層の2倍程度である。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="65" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>R1本-04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ⅲ-4</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>建築環境・設備・建築物衛生管理</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>日照・日射・採光</t>
         </is>
       </c>
-      <c r="E2" s="47" t="n">
+      <c r="E5" t="n">
         <v>1</v>
       </c>
-      <c r="F2" s="48" t="inlineStr">
-        <is>
-          <t>日射遮蔽、天空日照、直達日射量および窓ブラインド等による日射調整に関する正誤判定</t>
-        </is>
-      </c>
-      <c r="G2" s="48" t="inlineStr">
-        <is>
-          <t>日照及び日射に関する次の記述のうち，最も不適切なものはどれか。</t>
-        </is>
-      </c>
-      <c r="H2" s="48" t="inlineStr">
-        <is>
-          <t>① 大気圏外の太陽放射スペクトルは，赤外線域が最も大きく，可視光線や紫外線は含まれない。</t>
-        </is>
-      </c>
-      <c r="I2" s="48" t="inlineStr">
-        <is>
-          <t>② 天空日射量は，太陽放射が大気中の空気分子や浮遊粒子によって散乱されて地表に届く量である。</t>
-        </is>
-      </c>
-      <c r="J2" s="48" t="inlineStr">
-        <is>
-          <t>③ 直達日射量は，太陽から受照面に直接到達する太陽放射量である。</t>
-        </is>
-      </c>
-      <c r="K2" s="48" t="inlineStr">
-        <is>
-          <t>④ 南向き垂直面が受ける直達日射量は，冬至の正午頃に最大となる。</t>
-        </is>
-      </c>
-      <c r="L2" s="48" t="inlineStr">
-        <is>
-          <t>⑤ 外部日射遮蔽部材（ルーバー等）は，内部ブラインドよりも日射遮蔽効果が高い。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="65" customHeight="1">
-      <c r="A3" s="32" t="inlineStr">
-        <is>
-          <t>R1本-02</t>
-        </is>
-      </c>
-      <c r="B3" s="32" t="inlineStr">
-        <is>
-          <t>Ⅲ-2</t>
-        </is>
-      </c>
-      <c r="C3" s="32" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>実効放射量、集合住宅の隣棟間隔係数、熱線吸収ガラス、直接昼光率および頂側窓</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>日照・日射に関する次の記述のうち，最も不適切なものはどれか。</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>① 実効放射量（夜間放射量）は，雲があるときは，雲がないときに比較して増加する。</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>② 東西に長い集合住宅において，東京で日照時間を4時間確保するための隣棟間隔係数（隣棟間隔d／建物高さh）は，2程度となる。</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>③ 熱線吸収ガラスは，冷房時に効果がある。</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>④ 対向建物などがない場合は，ガラスのない開放された窓では，近似的に直接昼光率と立体角投射率［%］は一致する。</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>⑤ 頂側窓は，昼光によって展示品を鑑賞したい美術館の展示室や面積の大きい工場に用いられる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="65" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>R1本-05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Ⅲ-5</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>建築環境・設備・建築物衛生管理</t>
         </is>
       </c>
-      <c r="D3" s="32" t="inlineStr">
-        <is>
-          <t>照度・光環境</t>
-        </is>
-      </c>
-      <c r="E3" s="42" t="n">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>遮音・音環境</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>障壁の回折効果、残響時間、多孔質吸音材の吸音特性、重量衝撃音およびコインシデンス効果</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>音環境に関する次の記述のうち，最も不適切なものはどれか。</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>① 障壁は，回折による高音域の遮断に対する効果が大きい。</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>② 音響エネルギー密度が60dBだけ減衰するのに要する時間を残響時間という。</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>③ 多孔質材の吸音機構において，剛壁に直貼りしたときの吸音率は，吸音材の材厚を厚くしても，低音域の吸音率は向上しない。</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>④ 重量衝撃音の低減に対しては，床構造の曲げ剛性や質量が重要で，木造などの軽量床の場合，必要な性能を得ることは困難である。</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>⑤ コインシデンス効果は，音がさまざまな方向から壁面に入射する場合には広い周波数で発生する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="65" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>R1本-06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ⅲ-6</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>建築環境・設備・建築物衛生管理</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>換気・自然換気</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>自然換気（開口部通過風量、実効面積・流量係数、中性帯位置、風圧係数、温度差換気量）</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>自然換気に関する次の記述のうち，最も不適切なものはどれか。</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>① 窓を開放した場合などの開口部通過風量は，開口部面積に比例し，圧力差の平方根に比例する。</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>② 実効面積αAにおけるαは流量係数であり，開口の形状や寸法で異なるが，通常端部が直角に整形された窓では0.6〜0.7程度となる。</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>③ 中性帯の位置は，定性的には開口部の大きい方に近づく。</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>④ 2つの開口部があるとき，2つの開口部とも負の風圧係数となる場合，それらの風圧係数に差があっても風力換気は生じない。</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>⑤ 高さの異なる2つの開口部があるときの温度差換気量は，直列合成した実効面積αAに比例するとともに，室内外温度差及び開口高さの差の平方根に比例して増加する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="65" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>R1本-07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ⅲ-7</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>建築環境・設備・建築物衛生管理</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>水配管・ポンプ</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>水配管（開放式・密閉式ポンプ動力、二方弁・三方弁制御、管摩擦抵抗、リバースリターン、管内流速）</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>水配管に関する次の記述のうち，最も不適切なものはどれか。</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>① 開放式は必ず摩擦抵抗のほかに押し上げ揚程が加わり，密閉式に比べてポンプ動力が大きくなる。</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>② 二方弁制御は三方弁制御に比べて一般に制御性が良く，ポンプの台数制御などによりポンプの消費電力を節約できる。</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>③ 満水状態で流体が流れる場合の直管部摩擦抵抗は，管の長さと流体の密度及び流速の2乗に比例し，管の内径と管摩擦係数に反比例する。</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>④ リバースリターン方式では，各機器を通る配管長さが等しく，抵抗が同じとなるために，流量が自然に均一になるという特徴がある。</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>⑤ 普通の屋内配管では，侵食を防ぐための管内流速を一般に2.0m／s以下としている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="65" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>R1本-08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ⅲ-8</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>建築環境・設備・建築物衛生管理</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>省エネルギーシステム</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>省エネルギー設備（全熱交換器バイパス、蓄熱槽システム、コージェネレーション、太陽電池、COP定義）</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>省エネルギー設備機器に関する次の記述のうち，最も不適切なものはどれか。</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>① 空気調和機に使用する全熱交換器では，外気冷房が可能なときに給排気バイパスなどにより熱交換を回避する。</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>② 夜間電力利用の蓄熱槽システムでは，熱源の夜間運転時間が長いほど，熱源容量は小さくて済む。</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>③ コージェネレーションシステムは，ガスタービンやガスエンジン，燃料電池などを用いて電力エネルギーと熱エネルギーの両者を同時に供給するシステムであり，総合効率は最大80%程度まで期待することができる。</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>④ 多結晶シリコン太陽電池は，単結晶シリコン太陽電池と比較して変換効率が低いが，製造が容易で効率とコストのバランスが良いため，よく普及している太陽電池である。</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>⑤ ヒートポンプの冷房時の成績係数（COP）は，圧縮仕事に対する凝縮熱量の比で表す。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="65" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>R1本-09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ⅲ-9</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>建築環境・設備・建築物衛生管理</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>給水設備</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
         <v>1</v>
       </c>
-      <c r="F3" s="33" t="inlineStr">
-        <is>
-          <t>点光源からの水平面照度計算、グレア防止、昼光率および視環境・明視条件に関する正誤判定</t>
-        </is>
-      </c>
-      <c r="G3" s="33" t="inlineStr">
-        <is>
-          <t>光環境及び照明基本単位に関する次の記述のうち，最も不適切なものはどれか。</t>
-        </is>
-      </c>
-      <c r="H3" s="33" t="inlineStr">
-        <is>
-          <t>① 照度（lx）は光源の明るさそのものを示し，光度（cd）は照射された面の明るさを示す。</t>
-        </is>
-      </c>
-      <c r="I3" s="33" t="inlineStr">
-        <is>
-          <t>② 昼光率は，室内作業面照度の全天空照度に対する割合（%）である。</t>
-        </is>
-      </c>
-      <c r="J3" s="33" t="inlineStr">
-        <is>
-          <t>③ 光束の単位はルーメン（lm）である。</t>
-        </is>
-      </c>
-      <c r="K3" s="33" t="inlineStr">
-        <is>
-          <t>④ グレアは，高輝度な光源が視野内に存在することで生じる不快感や視認性低下である。</t>
-        </is>
-      </c>
-      <c r="L3" s="33" t="inlineStr">
-        <is>
-          <t>⑤ タスク・アンビエント照明は，全般照明と局所照明を組み合わせて省エネを図る。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="65" customHeight="1">
-      <c r="A4" s="46" t="inlineStr">
-        <is>
-          <t>R1本-03</t>
-        </is>
-      </c>
-      <c r="B4" s="46" t="inlineStr">
-        <is>
-          <t>Ⅲ-3</t>
-        </is>
-      </c>
-      <c r="C4" s="46" t="inlineStr">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>給水設備（高置水槽容量、受水槽有効容量、貯水槽点検スペース、クロスコネクション、給水圧力上限）</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>給水設備に関する次の記述のうち，最も不適切なものはどれか。</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>① 高置水槽容量は，揚水ポンプの能力との関係によっても異なるが，一般に1日の使用水量の1／3程度とすることが多い。</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>② 受水槽の有効容量は，水道事業者が断水を考慮して指定要綱などで設計用給水量の4／10〜6／10程度の容量を確保するところが多く，概算で1日の使用水量の1／2程度としている。</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>③ 貯水槽はすべての面から点検できるように水槽の上面に1.0m以上，側面と下面に0.6m以上の空間を確保して設置する。</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>④ 井戸を使っている住宅などで，井戸水の配管と水道配管を接続させることはクロスコネクションとなる。</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>⑤ 一般に給水管の給水圧力の上限値は，ホテル・集合住宅で300〜400kPa程度，事務所・工場では400〜500kPa程度として計画する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="65" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>R1本-10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ⅲ-10</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>建築環境・設備・建築物衛生管理</t>
         </is>
       </c>
-      <c r="D4" s="46" t="inlineStr">
-        <is>
-          <t>伝熱・熱伝導・熱移動</t>
-        </is>
-      </c>
-      <c r="E4" s="47" t="n">
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ポンプ・ファン</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>ポンプ及びファン（ラインポンプ、クロスフローファン、遠心ポンプ諸特性、シロッコ/ターボファン、渦巻きポンプ固定案内羽根）</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ポンプ及びファンに関する次の記述のうち，最も不適切なものはどれか。</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>① ラインポンプは小規模な冷温水循環用として配管途中に直接取り付けられるものである。</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>② クロスフローファンはエアコン，ファンコイルユニット，室内空気のサーキュレーターなど機器組込みの低圧ファンとして利用されている。</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>③ 遠心ポンプの流量と揚程は羽根車の毎分回転数で変化するが，流量は回転数に比例し，揚程は回転数の2乗に比例する。また，軸動力は回転数の3乗に比例する。</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>④ 空調用の送風機は高い省エネルギー性を求める場合，多翼型のシロッコファンよりも効率の高い後曲型のターボファンを使用する例が増えている。</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>⑤ 渦巻きポンプには羽根車の外に流れの乱れを防ぎポンプ効率を改善するための固定案内羽根がある。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="65" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>R1本-11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ⅲ-11</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>建築環境・設備・建築物衛生管理</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ボイラー設備</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>ボイラー（ボイラー容量・単位、真空式温水機、貫流式ボイラー、鋳鉄製ボイラー、都市ガス燃料）</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ボイラーに関する次の記述のうち，最も不適切なものはどれか。</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>① ボイラーの容量は，定格出力すなわち最大連続負荷における毎時出力によって表され，蒸気ボイラーの場合は換算蒸発量［kg／h］又は実際蒸発量［kg／h］，温水ボイラーの場合は熱出力［kW］で表すのが通常である。</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>② 真空式温水機は，鋼板製若しくは鋳鉄製のボイラーの大きな蒸気室に熱交換用のコイルをいくつか配置し，ボイラー内部の蒸気で間接的に暖房用水，給湯用水，プールの水などいくつかの系統の温水を1つのボイラーで加熱するものである。</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>③ 貫流式ボイラーは，燃焼室を取り巻く水管を給水が通過する間に，完全に蒸発する比較的小容量の蒸気ボイラーで，構造が簡単で効率も高く，安価なためにビルや工場などで用いられる。</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>④ 鋳鉄製ボイラーは大容量の高圧型ボイラーで，排気ガスによる給水加熱器又は燃焼空気予熱器などを用いるためボイラー効率は高く，大規模ビルや地域冷暖房プラントなどで用いられる。</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>⑤ ボイラーの排気ガスは地方自治体によってSOx，NOx，煤塵量などが規制されており，市街地でのボイラーの燃料は都市ガスを採用することが多い。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="65" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>R1本-12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ⅲ-12</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>建築環境・設備・建築物衛生管理</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>防災・消火設備</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>消火設備（火災分類A〜D、消防設備区分、屋内消火栓放水圧力、屋外消火栓有効階、ドレンチャー設備）</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>消火設備に関する次の記述のうち，最も不適切なものはどれか。</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>① 火災は，A火災（普通火災），B火災（油火災），C火災（電気火災），D火災（金属火災）に区分される。</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>② 消防の用に供する設備は，消火設備，警報設備，避難設備の3つに分類される。</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>③ 屋内消火栓設備のホース先端における放水圧力は7MPaを超えないように規定されている。</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>④ 屋外消火栓設備は，1階及び2階の床面積の広い建物に設置し，屋外から屋内に向けて放水によって消火する設備であり，1階及び2階の部分に限って有効な消火設備である。</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>⑤ ドレンチャー消火設備は，建物外部の火災に対し外壁，屋根，開口部に水幕をつくって延焼を防ぐための設備である。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="65" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>R1本-13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ⅲ-13</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>建築環境・設備・建築物衛生管理</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>結露・結露防止対策</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>住宅の断熱・結露防止（夏型結露、通気構法・防風層、防湿層位置、材料内水蒸気移動、湿気伝導率）</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>戸建て住宅の断熱と結露防止に関する次の記述のうち，最も不適切なものはどれか。</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>① 夏型結露は，構造用合板や外壁材に含まれている水分が日射で加熱され，壁体内を透過して防湿層裏面で結露する現象などをいう。</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>② 繊維状の断熱材を用いた外壁の通気構法には，断熱材内に冷たい外気が侵入しないよう，防風層の設置が必要である。</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>③ 冬季の結露を防止するために，壁体内に設ける防湿層は，温度の低い，断熱材の外気側に配置しなくてはならない。</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>④ 材料内の湿気移動は，含湿率があまり高く見られない場合には水蒸気の形で行われ，水蒸気圧の高い方から低い方へ流れる。</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>⑤ 均質でない建築材料の湿気伝導率λ'を，透湿係数Pと厚さδから逆算してはならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="65" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>R1本-14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ⅲ-14</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>建築環境・設備・建築物衛生管理</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>加湿・除湿装置</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>加湿器の各種方式（パン形、気化式、スプレー形、遠心加湿器、超音波加湿器）の特徴と正誤判定</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>加湿器に関する次の記述のうち，最も不適切なものはどれか。</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>① パン形加湿器は，水中に溶けた不純物が濃縮されるため，スケールが付着し，寿命が短い。</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>② 気化式加湿器には，加湿装置についた残留物の洗浄用に加湿量の1.5〜3倍の給水量が必要である。</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>③ スプレー形加湿器は，水や温水噴霧の場合には温度低下を伴う。</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>④ 遠心加湿器は，水を回転拡散させ，霧状にして給湿する。</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>⑤ 超音波加湿器は，常温で霧化するため，冷房時より暖房時の加湿に適する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="65" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>R1本-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ⅲ-15</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>建築環境・設備・建築物衛生管理</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>室内環境・化学物質</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
         <v>2</v>
       </c>
-      <c r="F4" s="48" t="inlineStr">
-        <is>
-          <t>壁体の熱伝達率、熱貫流率、熱伝導率および熱移動メカニズムに関する基本記述の正誤判定</t>
-        </is>
-      </c>
-      <c r="G4" s="48" t="inlineStr">
-        <is>
-          <t>壁体の熱移動に関する次の記述のうち，最も不適切なものはどれか。</t>
-        </is>
-      </c>
-      <c r="H4" s="48" t="inlineStr">
-        <is>
-          <t>① 熱伝導率は，物質固有の熱の伝えやすさを示す指標である。</t>
-        </is>
-      </c>
-      <c r="I4" s="48" t="inlineStr">
-        <is>
-          <t>② 壁の熱抵抗は，熱伝導率に壁の厚さを乗じることで算出される。</t>
-        </is>
-      </c>
-      <c r="J4" s="48" t="inlineStr">
-        <is>
-          <t>③ 熱貫流率は，熱抵抗の逆数として計算される。</t>
-        </is>
-      </c>
-      <c r="K4" s="48" t="inlineStr">
-        <is>
-          <t>④ 外断熱は，構造躯体を保温するため熱橋対策に有効である。</t>
-        </is>
-      </c>
-      <c r="L4" s="48" t="inlineStr">
-        <is>
-          <t>⑤ 中空層の熱抵抗は，放射と空気の対流伝熱によって決まる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="65" customHeight="1">
-      <c r="A5" s="32" t="inlineStr">
-        <is>
-          <t>R1本-04</t>
-        </is>
-      </c>
-      <c r="B5" s="32" t="inlineStr">
-        <is>
-          <t>Ⅲ-4</t>
-        </is>
-      </c>
-      <c r="C5" s="32" t="inlineStr">
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ホルムアルデヒド放散速度の計算（室容積30m³、換気回数0.5/h、外気濃度5μg/m³、室内定常濃度20μg/m³、面積25m²）</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>室内において，ホルムアルデヒドが単一の材料から放散するとき，下記の条件における材料の放散速度に最も近いものはどれか。ただし，材料の放散速度は気中濃度の影響を受けないものとし，発生したホルムアルデヒドは，瞬時に一様拡散し，吸着・分解せず，室内濃度に変動はなく安定しているものとする。
+条件：（1）室の容積：30m³、（2）室の換気回数：0.5回／h、（3）外気中のホルムアルデヒド濃度：5μg／m³、（4）室内空気中のホルムアルデヒド定常濃度：20μg／m³、（5）ホルムアルデヒド放散面積：25m²</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>① 6 μg／m²h</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>② 9 μg／m²h</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>③ 12 μg／m²h</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>④ 18 μg／m²h</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>⑤ 21 μg／m²h</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="65" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>R1本-16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ⅲ-16</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>建築環境・設備・建築物衛生管理</t>
         </is>
       </c>
-      <c r="D5" s="32" t="inlineStr">
-        <is>
-          <t>遮音・音環境</t>
-        </is>
-      </c>
-      <c r="E5" s="42" t="n">
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>ヒートアイランド現象</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ヒートアイランド現象（原因、ダストドーム形成、光化学オキシダント・集中豪雨、生物多様性・媒介生物、冬季暖房影響）</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ヒートアイランド現象の原因とその影響に関する次の記述のうち，最も不適切なものはどれか。</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>① ヒートアイランド現象の原因としては，人工排熱の増加，緑地・水面の減少と地表面の人工化，都市形態の高密度化が挙げられる。</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>② ヒートアイランド現象による都市域の高温化により発生する上昇気流が温度層に遮られて生じる混合層（ダストドーム）を形成することが指摘されている。</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>③ ヒートアイランド現象は，光化学オキシダント生成を助長するほか，局地的集中豪雨との関連性も指摘されている。</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>④ ヒートアイランド現象は，都市部における生物多様性に影響を与える可能性があり，感染症を媒介する生物の分布・個体数の変化などによる影響も懸念される。</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>⑤ ヒートアイランド現象は，冬季においては大都市部を中心として気温の上昇が顕著であり，暖房エネルギーを削減する影響も報告されている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="65" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>R1本-17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ⅲ-17</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>建築環境・設備・建築物衛生管理</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ねずみ・害虫対策</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>建築物におけるねずみ・害虫対策（ねずみ駆除基本、ゴキブリ体内時計、ハエ類発生源、ダニのアレルゲン、昆虫侵入）</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>建築物におけるねずみ・害虫対策に関する次の記述のうち，最も不適切なものはどれか。</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>① ねずみの駆除は，餌を断つこと，通路を遮断すること，巣を作らせないことを基本に進める。</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>② ゴキブリは，夜間，潜伏場所から出現し，摂食，摂水行動を起こし，体内に組み込まれた体内時計により，約24時間を周期とする行動がみられる。</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>③ イエバエ，クロバエ，ニクバエ類等の中・大型のハエ類は，厨房等の処理が適切に行われていても，幼虫が発生する。</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>④ 居住環境で見られるコナヒョウヒダニやヤケヒョウヒダニは，ヒトを刺したり吸血したりすることはないが，そのふんや死骸は喘息やアトピー性皮膚炎の原因となることがある。</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>⑤ 外気温が低くなると，外壁に内部から伝わる熱や，隙間から漏れる熱を感じて，越冬等の目的で昆虫等が侵入しやすくなる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="65" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>R1本-18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ⅲ-18</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>水質管理</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>水質指標・用語単位</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>生活排水処理施設の用語と単位の組合せ（水面積負荷、ばっ気強度、越流負荷、比表面積、BOD-MLSS負荷）</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>生活排水処理施設の設計又は維持管理において用いられる用語と単位の組合せとして，次のうち最も不適切なものはどれか。</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>① 水面積負荷 ── m³／(m²・日)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>② ばっ気強度 ── m³／(m³・時)</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>③ 越流負荷 ── m³／(m²・時)</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>④ 比表面積 ── m²／m³</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>⑤ BOD−MLSS負荷 ── kg／(kg・日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="65" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>R1本-19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ⅲ-19</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>水質管理</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>水質試験・BOD測定</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>排水のBOD測定方法（硝化抑制、20℃・5日間、希釈水栄養素、溶存酸素消費率、過飽和ばっ気）</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>排水の水質試験におけるBOD（生物化学的酸素要求量）の測定に関する次の記述のうち，最も不適切なものはどれか。</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>① 硝化作用を抑制した状態のBODの測定方法が定められている。</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>② 試料を希釈水で希釈し，20℃で5日間放置したとき消費された溶存酸素量から求める。</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>③ 希釈水には，好気性微生物の正常な発育に必要な微量の培養素（カルシウム，マグネシウム，鉄，窒素，りん等）を含有していること。</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>④ 溶存酸素消費率が100%になるように試料を希釈する。</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>⑤ 溶存酸素が過飽和の試料は，ばっ気などにより，溶存酸素を20℃の飽和量近くにする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="65" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>R1本-20</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ⅲ-20</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>水質管理</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>浄化槽の構造・処理方式</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>5</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>浄化槽の構造基準に規定されている処理方式（標準活性汚泥方式）選定</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>浄化槽の構造基準（昭和55年建設省告示第1292号 最終改正平成18年国土交通省告示第154号に定める構造方法）に規定されている処理方式は，次のうちどれか。</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>① 担体流動方式</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>② 膜分離活性汚泥方式</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>③ 回分式活性汚泥方式</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>④ オキシデーションディッチ方式</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>⑤ 標準活性汚泥方式</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="65" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>R1本-21</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ⅲ-21</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>水質管理</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>水質管理・消毒</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>処理水の消毒（紫外線消毒、遊離塩素pH影響、塩素存在形態、オゾン残留性、オゾン消毒力）</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>処理水の消毒に関する次の記述のうち，最も適切なものはどれか。</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>① 紫外線消毒は，浮遊物質が多い水に適している。</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>② 遊離塩素の消毒力は，pHの影響を顕著に受ける。</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>③ 塩素の消毒力は，塩素の存在形態にかかわらずほぼ一定である。</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>④ オゾン消毒は，効果の残留性がある。</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>⑤ オゾンの消毒力は，塩素より弱い。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="65" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>R1本-22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ⅲ-22</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>水質管理</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>水質環境基準・適用水域</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="33" t="inlineStr">
-        <is>
-          <t>残響時間計算、空気音・床衝撃音遮音性能、コインシデンス効果および吸音機構に関する正誤判定</t>
-        </is>
-      </c>
-      <c r="G5" s="33" t="inlineStr">
-        <is>
-          <t>音環境に関する次の記述のうち，最も不適切なものはどれか。</t>
-        </is>
-      </c>
-      <c r="H5" s="33" t="inlineStr">
-        <is>
-          <t>① 透過損失が大きい壁ほど，音をよく通しやすいことを意味する。</t>
-        </is>
-      </c>
-      <c r="I5" s="33" t="inlineStr">
-        <is>
-          <t>② 一重壁の空気音遮音は，面密度が大きいほど効果が高くなる（質量法則）。</t>
-        </is>
-      </c>
-      <c r="J5" s="33" t="inlineStr">
-        <is>
-          <t>③ 残響時間は室容積に比例し，等価吸音面積に反比例する（サビンの式）。</t>
-        </is>
-      </c>
-      <c r="K5" s="33" t="inlineStr">
-        <is>
-          <t>④ 多孔質材料は，高音域の吸音に適している。</t>
-        </is>
-      </c>
-      <c r="L5" s="33" t="inlineStr">
-        <is>
-          <t>⑤ 音の屈折現象は，空気中の温度勾配や風速分布によって生じる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="46" t="inlineStr">
-        <is>
-          <t>R1本-05</t>
-        </is>
-      </c>
-      <c r="B6" s="46" t="inlineStr">
-        <is>
-          <t>Ⅲ-5</t>
-        </is>
-      </c>
-      <c r="C6" s="46" t="inlineStr">
-        <is>
-          <t>建築環境・設備・建築物衛生管理</t>
-        </is>
-      </c>
-      <c r="D6" s="46" t="inlineStr">
-        <is>
-          <t>結露・結露防止対策</t>
-        </is>
-      </c>
-      <c r="E6" s="47" t="n">
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>生活環境項目と適用水域の組合せ（BOD-湖沼、COD-海域、pH-河川、大腸菌群数-湖沼、DO-海域）</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>生活環境の保全に関する環境基準項目と適用される水域の組合せとして，最も不適切なものはどれか。</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>① 生物化学的酸素要求量（BOD） ── 湖沼</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>② 化学的酸素要求量（COD） ── 海域</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>③ 水素イオン濃度（pH） ── 河川</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>④ 大腸菌群数 ── 湖沼</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>⑤ 溶存酸素量（DO） ── 海域</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="65" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>R1本-23</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ⅲ-23</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>水質管理</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>長時間ばっ気方式・計算</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>4</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>長時間ばっ気方式の計算・評価（流入BOD量24kg/日、HRT 16h、BOD容積負荷0.30kg/(m³・日)、返送率125%/150%、BOD除去率95%）</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>下図に示す長時間ばっ気方式の汚水処理施設に関する次の記述のうち，最も不適切なものはどれか。
+［条件・フロー図：流入120m³/日・BOD200mg/L、ばっ気槽80m³、返送汚泥150m³/日、放流120m³/日・BOD10mg/L］</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>① ばっ気槽の水力学的滞留時間（HRT）は，16時間である。</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>② 施設への流入BOD量は，24kg／日である。</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>③ ばっ気槽のBOD容積負荷は，0.30kg／(m³・日)である。</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>④ ばっ気槽への汚泥返送率は，150%である。</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>⑤ 施設全体としてのBOD除去率は，95%である。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="65" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>R1本-24</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ⅲ-24</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>廃棄物管理</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>リサイクル関連法・公布順</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>4</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>昭和以降の廃棄物・リサイクル関連法の公布年月日順並べ替え（廃掃法→再生資源利用促進法→特定有害廃棄物輸出入規制法→容器包装リサイクル法→循環型社会基本法）</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>我が国の昭和以降の廃棄物・リサイクル関連法制度について，次の（ア）〜（オ）の法律の公布年月日が古いものから順に並べられたものはどれか。
+（ア）循環型社会形成推進基本法
+（イ）廃棄物の処理及び清掃に関する法律
+（ウ）再生資源の利用の促進に関する法律
+（エ）特定有害廃棄物等の輸出入等の規制に関する法律
+（オ）容器包装に係る分別収集及び再商品化の促進等に関する法律</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>① ア → イ → オ → ウ → エ</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>② ア → イ → エ → オ → ウ</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>③ イ → ウ → エ → ア → オ</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>④ イ → ウ → エ → オ → ア</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>⑤ イ → オ → ア → ウ → エ</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="65" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>R1本-25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Ⅲ-25</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>廃棄物管理</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>ごみ排出・統計数値</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
         <v>3</v>
       </c>
-      <c r="F6" s="48" t="inlineStr">
-        <is>
-          <t>内部結露・表面結露の発生メカニズムおよび断熱・防湿層設置等の防止対策に関する正誤判定</t>
-        </is>
-      </c>
-      <c r="G6" s="48" t="inlineStr">
-        <is>
-          <t>結露現象及びその防止対策に関する次の記述のうち，最も不適切なものはどれか。</t>
-        </is>
-      </c>
-      <c r="H6" s="48" t="inlineStr">
-        <is>
-          <t>① 表面結露は，壁面温度が室内空気の露点温度以下になると発生する。</t>
-        </is>
-      </c>
-      <c r="I6" s="48" t="inlineStr">
-        <is>
-          <t>② 内部結露は，壁体内部を拡散する水蒸気が冷やされることで生じる。</t>
-        </is>
-      </c>
-      <c r="J6" s="48" t="inlineStr">
-        <is>
-          <t>③ 冬期の結露防止用防湿層は，壁体の外気側（低温側）に設置する。</t>
-        </is>
-      </c>
-      <c r="K6" s="48" t="inlineStr">
-        <is>
-          <t>④ 断熱性の向上は，壁体内表面温度を高めて表面結露を防ぐ。</t>
-        </is>
-      </c>
-      <c r="L6" s="48" t="inlineStr">
-        <is>
-          <t>⑤ 換気により室内の水蒸気圧を下げることが有効である。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="32" t="inlineStr">
-        <is>
-          <t>R1本-06</t>
-        </is>
-      </c>
-      <c r="B7" s="32" t="inlineStr">
-        <is>
-          <t>Ⅲ-6</t>
-        </is>
-      </c>
-      <c r="C7" s="32" t="inlineStr">
-        <is>
-          <t>建築環境・設備・建築物衛生管理</t>
-        </is>
-      </c>
-      <c r="D7" s="32" t="inlineStr">
-        <is>
-          <t>日射・熱移動</t>
-        </is>
-      </c>
-      <c r="E7" s="42" t="n">
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>平成29年度の1人1日当たりごみ排出量（920g）と平成24年度対比（44g減少）の穴埋め</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>我が国の廃棄物の発生量に関する次の記述の，［　］に入る数量の組合せとして最も適切なものはどれか。
+「一般廃棄物の排出及び処理状況等（平成29年度）について」によると，平成29年度における1人1日当たりのごみ排出量は［ ア ］グラムである。平成24年度と比べると，［ イ ］グラム［ ウ ］している。</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>① 1,033 ／ 260 ／ 増加</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>② 1,033 ／ 260 ／ 減少</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>③ 920 ／ 44 ／ 減少</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>④ 920 ／ 44 ／ 増加</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>⑤ 1,033 ／ 44 ／ 減少</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="65" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>R1本-26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Ⅲ-26</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>廃棄物管理</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>廃棄物処理法・基本原則</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>廃棄物処理法（目的、市町村の一般廃棄物計画・収集処分、排出事業者責任、処理委託、特別管理産業廃棄物定義）</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>廃棄物の処理及び清掃に関する法律（廃棄物処理法）に関する次の記述のうち，最も不適切なものはどれか。</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>① 法律の目的は，汚物を衛生的に処理し，生活環境を清潔にすることにより，公衆衛生の向上を図ることである。</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>② 市町村は，一般廃棄物の処理計画を定め，その区域内の一般廃棄物を収集，処理処分しなければならない。</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>③ 産業廃棄物の処理は，汚染者負担の原則に基づいて排出事業者自身に処理責任がある。</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>④ 産業廃棄物の処理は，都道府県知事の許可を得た処理業者に委託することができる。</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>⑤ 特別管理産業廃棄物とは，産業廃棄物のうち，爆発性，毒性，感染性その他の人の健康又は生活環境に係る被害を生ずるおそれがある性状を有するものとして政令で定めるものをいう。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="65" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>R1本-27</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Ⅲ-27</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>廃棄物管理</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>有害廃棄物・PCB</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>2</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>PCB（ポリ塩化ビフェニル）の性質、異性体、水溶性・安定性、用途、カネミ油症事件</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>PCB（ポリ塩化ビフェニル）に関する次の記述のうち，最も不適切なものはどれか。</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>① PCBの構造は，塩素の位置と数によって多くの異性体がある。</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>② 化学的に安定で，酸・アルカリに侵されず，水によく溶ける。</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>③ PCBは，変圧器や熱交換器で使用するための安定した熱媒体として開発された。</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>④ 不燃性で加熱・冷却しても性質が変わらない。</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>⑤ 福岡県で米ぬか油にPCBが漏れて混入し，カネミ油症事件が起きた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="65" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>R1本-28</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Ⅲ-28</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>廃棄物管理</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ダイオキシン類対策・焼却温度</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>5</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>廃棄物焼却温度（燃焼室内温度800〜900℃、ダイオキシン抑熱800℃以上、溶融950℃超、悪臭分解700℃以上、Thermal NOx 1000〜1300℃超）</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>廃棄物の焼却温度に関する次の記述のうち，最も不適切なものはどれか。</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>① 廃棄物焼却炉における燃焼室内温度は，通常800〜900℃程度に保たれている。</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>② ダイオキシン類の生成を抑えるには，800℃以上が必要とされる。</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>③ 950℃を超えると焼却灰の溶融が起こり，炉壁や冷却装置などに付着する可能性がある。</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>④ 悪臭物質（アンモニアやメチルメルカプタンなど）や有害物質（ホルムアルデヒドやシアン化水素など）の分解には，700℃以上が必要とされる。</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>⑤ 750℃以下になると空気中の窒素と酸素が反応して，いわゆるThermal NOxが発生する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="65" customHeight="1">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>R1本-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Ⅲ-29</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>廃棄物管理</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>廃棄物選別技術</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>廃棄物の選別技術（ふるい選別・トロンメル、渦電流選別・導電性金属選別、磁力選別、手選別、比重選別）</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>廃棄物の選別技術に関する次の記述のうち，最も適切なものはどれか。</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>① ふるい選別には，トロンメルや振動ふるいなどの方式があるが，いずれも選別精度が高く効果的な選別ができる。</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>② 渦電流選別は，鉄が除かれた混合ごみから，非鉄金属とプラスチック等の電流を通さない（非導電性）物質を選別する技術である。</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>③ 磁力選別は選別精度が高いため，金属類と有機系のごみとの混合ごみからでもダスト等の混入のない高純度の資源を得られるので，それらをあらかじめ分別等をしておくことはない。</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>④ 手選別による廃棄物の選別は，コスト，効率の点で不利なので，今日の我が国の廃棄物処理では，ほとんど行われていない。</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>⑤ 比重選別はごみの比重の違いで選別する方法であり，廃棄物処理では液体中での比重差で分離する方法が一般的である。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="65" customHeight="1">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>R1本-30</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Ⅲ-30</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>廃棄物管理</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>ごみ処理・統計数値</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>3</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2017年度の一般廃棄物処理における中間処理率（94%）、総資源化率（20%）、最終処分率（3%）の数値選定</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>一般廃棄物に関する次の記述の，［　］に入る数値の組合せとして，最も適切なものはどれか。
+2017年度の一般廃棄物の処理において，総処理量に対する中間処理量の割合は，［ A ］%である。また，総資源化量（中間処理後の再生利用を含めた量）と最終処分量の割合は総排出量に対し，それぞれ［ B ］%，［ C ］%である。</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>① 84 ／ 20 ／ 5</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>② 84 ／ 30 ／ 3</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>③ 94 ／ 20 ／ 9</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>④ 94 ／ 30 ／ 5</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>⑤ 94 ／ 20 ／ 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="65" customHeight="1">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>R1本-31</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Ⅲ-31</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>廃棄物管理</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>最終処分場の構造・維持管理</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>3</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>一般廃棄物・産業廃棄物管理型最終処分場の構造（準好気性埋立構造、浸出水集排水施設、遮水工・二重遮水工等、浸出水調整池、被覆型処分場）</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>一般廃棄物最終処分場及び産業廃棄物管理型最終処分場の主な施設に関する次の記述のうち，最も不適切なものはどれか。</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>① 日本においては，自然換気により好気性領域を拡大させる準好気性埋立構造の埋立地形式が主流である。</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>② 浸出水集排水施設とは，浸出水を速やかに集水し排水する機能と埋立地内の好気性ゾーンを拡大する機能を持つものである。</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>③ 遮水工は，地下水汚染防止の目的で設置されるものであり，表面遮水工のみの設置が義務付けられている。</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>④ 浸出水処理施設は，基本的に一定の処理量を前提に設計，運転されるため，浸出水量の変動を吸収するための浸出水調整池が設けられる。</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>⑤ 被覆型最終処分場とは，埋立地に屋根をかけたものであり，降雨が埋立地に入ることを制御できるため，浸出水処理の負担は軽い。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="65" customHeight="1">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>R1本-32</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Ⅲ-32</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>廃棄物管理</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>最終処分場・浸出水量計算</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
         <v>4</v>
       </c>
-      <c r="F7" s="33" t="inlineStr">
-        <is>
-          <t>日射遮蔽、天空日照、直達日射量および窓ブラインド等による日射調整に関する正誤判定</t>
-        </is>
-      </c>
-      <c r="G7" s="33" t="inlineStr">
-        <is>
-          <t>空調熱負荷に関する次の記述のうち，最も不適切なものはどれか。</t>
-        </is>
-      </c>
-      <c r="H7" s="33" t="inlineStr">
-        <is>
-          <t>① 顕熱負荷は温度上昇・下降を伴う熱負荷である。</t>
-        </is>
-      </c>
-      <c r="I7" s="33" t="inlineStr">
-        <is>
-          <t>② 潜熱負荷は状態変化（湿度変化）を伴う熱負荷である。</t>
-        </is>
-      </c>
-      <c r="J7" s="33" t="inlineStr">
-        <is>
-          <t>③ 外気負荷は，導入外気を室内状態まで加熱・冷却・加減湿する負荷である。</t>
-        </is>
-      </c>
-      <c r="K7" s="33" t="inlineStr">
-        <is>
-          <t>④ 躯体の蓄熱効果は熱負荷のピーク値を著しく引き上げる要因となる。</t>
-        </is>
-      </c>
-      <c r="L7" s="33" t="inlineStr">
-        <is>
-          <t>⑤ 人体からの放熱には，顕熱放熱と潜熱放熱の両方が含まれる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="46" t="inlineStr">
-        <is>
-          <t>R1本-07</t>
-        </is>
-      </c>
-      <c r="B8" s="46" t="inlineStr">
-        <is>
-          <t>Ⅲ-7</t>
-        </is>
-      </c>
-      <c r="C8" s="46" t="inlineStr">
-        <is>
-          <t>建築環境・設備・建築物衛生管理</t>
-        </is>
-      </c>
-      <c r="D8" s="46" t="inlineStr">
-        <is>
-          <t>温熱環境・温熱指標(PMV/WBGT)</t>
-        </is>
-      </c>
-      <c r="E8" s="47" t="n">
-        <v>3</v>
-      </c>
-      <c r="F8" s="48" t="inlineStr">
-        <is>
-          <t>作用温度(OT)、PMV、WBGT、新有効温度(ET*)等の温熱環境指標に関する記述の正誤判定</t>
-        </is>
-      </c>
-      <c r="G8" s="48" t="inlineStr">
-        <is>
-          <t>温熱環境指標に関する次の記述のうち，最も不適切なものはどれか。</t>
-        </is>
-      </c>
-      <c r="H8" s="48" t="inlineStr">
-        <is>
-          <t>① PMV は熱中症のみを評価する専門指標である。</t>
-        </is>
-      </c>
-      <c r="I8" s="48" t="inlineStr">
-        <is>
-          <t>② 作用温度（OT）は，気温と放射温度を考慮した指標である。</t>
-        </is>
-      </c>
-      <c r="J8" s="48" t="inlineStr">
-        <is>
-          <t>③ WBGT（暑さ指数）は，屋外では湿球温度・黒球温度・乾球温度から算出される。</t>
-        </is>
-      </c>
-      <c r="K8" s="48" t="inlineStr">
-        <is>
-          <t>④ 新有効温度（ET*）は相対湿度50%を基準とする指標である。</t>
-        </is>
-      </c>
-      <c r="L8" s="48" t="inlineStr">
-        <is>
-          <t>⑤ 代謝量（met）や着衣量（clo）はPMVの入力要素である。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="32" t="inlineStr">
-        <is>
-          <t>R1本-08</t>
-        </is>
-      </c>
-      <c r="B9" s="32" t="inlineStr">
-        <is>
-          <t>Ⅲ-8</t>
-        </is>
-      </c>
-      <c r="C9" s="32" t="inlineStr">
-        <is>
-          <t>建築環境・設備・建築物衛生管理</t>
-        </is>
-      </c>
-      <c r="D9" s="32" t="inlineStr">
-        <is>
-          <t>湿気環境・比エンタルピー</t>
-        </is>
-      </c>
-      <c r="E9" s="42" t="n">
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>オープン型最終処分場の日平均浸出水発生量（70m³/日）と浸出係数（0.6）の計算（面積2.5ha、降水量1700mm/年、蒸発散量2.0mm/日）</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>最終処分場の浸出水量に関する次の記述の，［　］に入る数値の組合せとして，最も適切なものはどれか。
+表面遮水工が設置されているオープン型最終処分場において，埋立面積が2.5ha，年間降水量が1700mm／年，蒸発散量が2.0mm／日の場合，日平均浸出水発生量は［ A ］m³／日，浸出係数は［ B ］である。ただし，埋立地に降った雨水が表流水として外部へ排除されることはないものとする。</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>① 50 ／ 0.4</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>② 50 ／ 0.6</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>③ 70 ／ 0.4</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>④ 70 ／ 0.6</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>⑤ 90 ／ 0.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="65" customHeight="1">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>R1本-33</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Ⅲ-33</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>廃棄物管理</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>環境影響評価・生活環境影響調査</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>廃棄物処理施設生活環境影響調査指針（義務付け施設、変更許可時も必要、動植物調査含まない、調査事項、縦覧・意見聴取手続）</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>「廃棄物処理施設生活環境影響調査指針（平成18年9月環境省）」に関する次の記述のうち，最も不適切なものはどれか。</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>① 生活環境影響調査は，許可を要するすべての廃棄物処理施設について実施が義務づけられている。</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>② 生活環境影響調査は，廃棄物処理施設の変更の許可を受ける場合は不要である。</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>③ 動物・植物調査は生活環境影響調査の対象とする調査事項には含まれていない。</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>④ 調査事項は，廃棄物処理施設の稼働並びに当該施設に係る廃棄物の搬出入及び保管に伴って生じる生活環境への影響に関するものである。</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>⑤ 廃棄物処理施設のうち，焼却施設及び最終処分場については，知事により申請書及び生活環境影響調査書が縦覧され，住民，市町村長の意見聴取，専門家の意見聴取等の手続が行われる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="65" customHeight="1">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>R1本-34</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Ⅲ-34</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>廃棄物管理</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>災害廃棄物対策</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
         <v>5</v>
       </c>
-      <c r="F9" s="33" t="inlineStr">
-        <is>
-          <t>建築環境・空調・給排水における技術基準および正誤判定</t>
-        </is>
-      </c>
-      <c r="G9" s="33" t="inlineStr">
-        <is>
-          <t>空気線図に関する次の記述のうち，最も不適切なものはどれか。</t>
-        </is>
-      </c>
-      <c r="H9" s="33" t="inlineStr">
-        <is>
-          <t>① 乾球温度と絶対湿度が決まれば，空気の状態点が定まる。</t>
-        </is>
-      </c>
-      <c r="I9" s="33" t="inlineStr">
-        <is>
-          <t>② 相対湿度は，水蒸気分圧の飽和水蒸気圧に対する割合である。</t>
-        </is>
-      </c>
-      <c r="J9" s="33" t="inlineStr">
-        <is>
-          <t>③ 加熱コイルでの加熱では，絶対湿度は変化しない。</t>
-        </is>
-      </c>
-      <c r="K9" s="33" t="inlineStr">
-        <is>
-          <t>④ 冷却減湿では，空気が露点以下まで冷却される。</t>
-        </is>
-      </c>
-      <c r="L9" s="33" t="inlineStr">
-        <is>
-          <t>⑤ 水噴霧加湿では，空気の乾球温度が急激に上昇する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="46" t="inlineStr">
-        <is>
-          <t>R1本-09</t>
-        </is>
-      </c>
-      <c r="B10" s="46" t="inlineStr">
-        <is>
-          <t>Ⅲ-9</t>
-        </is>
-      </c>
-      <c r="C10" s="46" t="inlineStr">
-        <is>
-          <t>建築環境・設備・建築物衛生管理</t>
-        </is>
-      </c>
-      <c r="D10" s="46" t="inlineStr">
-        <is>
-          <t>室内機器・顕熱発熱</t>
-        </is>
-      </c>
-      <c r="E10" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="48" t="inlineStr">
-        <is>
-          <t>建築環境・空調・給排水における技術基準および正誤判定</t>
-        </is>
-      </c>
-      <c r="G10" s="48" t="inlineStr">
-        <is>
-          <t>室内発生熱量に関する次の記述のうち，最も不適切なものはどれか。</t>
-        </is>
-      </c>
-      <c r="H10" s="48" t="inlineStr">
-        <is>
-          <t>① 室温が高くなると，人体からの放熱は潜熱量が減少し顕熱量が増加する。</t>
-        </is>
-      </c>
-      <c r="I10" s="48" t="inlineStr">
-        <is>
-          <t>② OA機器の発熱は，主に顕熱負荷となる。</t>
-        </is>
-      </c>
-      <c r="J10" s="48" t="inlineStr">
-        <is>
-          <t>③ 白熱灯は入力電力の大部分が熱となる。</t>
-        </is>
-      </c>
-      <c r="K10" s="48" t="inlineStr">
-        <is>
-          <t>④ 顕熱比（SHF）は，全熱負荷に対する顕熱負荷の割合である。</t>
-        </is>
-      </c>
-      <c r="L10" s="48" t="inlineStr">
-        <is>
-          <t>⑤ 厨房機器の燃焼ガスには水蒸気（潜熱）が含まれる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="32" t="inlineStr">
-        <is>
-          <t>R1本-10</t>
-        </is>
-      </c>
-      <c r="B11" s="32" t="inlineStr">
-        <is>
-          <t>Ⅲ-10</t>
-        </is>
-      </c>
-      <c r="C11" s="32" t="inlineStr">
-        <is>
-          <t>建築環境・設備・建築物衛生管理</t>
-        </is>
-      </c>
-      <c r="D11" s="32" t="inlineStr">
-        <is>
-          <t>パーソナル空調・空調方式</t>
-        </is>
-      </c>
-      <c r="E11" s="42" t="n">
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>大規模災害発生時における災害廃棄物対策行動指針（基本的考え方、市町村の固有事務、一次仮置場撤去、後工程・分別考慮、コンクリートくず早期処理）</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>「大規模災害発生時における災害廃棄物対策行動指針（平成27年11月 環境省大臣官房廃棄物・リサイクル対策部）」に関する次の記述のうち，最も不適切なものはどれか。</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>① この指針は，大規模災害発生時においても災害廃棄物を適正かつ円滑・迅速に処理するための基本的考え方，対応方針を整理するものである。</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>② 災害廃棄物の処理は市町村が行う固有事務として位置付けられている。</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>③ 大規模災害発生時に道路際や空地等に集積された廃棄物は，可能な限り分別した上で速やかに一次仮置場へ運搬，撤去する。</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>④ 災害廃棄物の選別に当たっては，後工程となる焼却処理や再生利用を効率的に行う観点から処理方針を検討する。</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>⑤ 災害廃棄物の処理期間は，地域及び災害廃棄物の特性に応じて柔軟に設定すべきものであるが，特にコンクリートくずは早期に処理すべきものである。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="65" customHeight="1">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>R1本-35</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Ⅲ-35</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>廃棄物管理</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>指定廃棄物・放射性物質</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
         <v>5</v>
       </c>
-      <c r="F11" s="33" t="inlineStr">
-        <is>
-          <t>VAV方式、床吹出し空調、全熱交換器、パッケージ空調等の方式比較と特徴に関する正誤判定</t>
-        </is>
-      </c>
-      <c r="G11" s="33" t="inlineStr">
-        <is>
-          <t>空調方式に関する次の記述のうち，最も不適切なものはどれか。</t>
-        </is>
-      </c>
-      <c r="H11" s="33" t="inlineStr">
-        <is>
-          <t>① CAV（定風量）方式は，送風量を一定に保つ。</t>
-        </is>
-      </c>
-      <c r="I11" s="33" t="inlineStr">
-        <is>
-          <t>② VAV（変風量）方式は，負荷に応じて風量を制御する。</t>
-        </is>
-      </c>
-      <c r="J11" s="33" t="inlineStr">
-        <is>
-          <t>③ 水―空気方式は，ダクトスペースを縮小できる。</t>
-        </is>
-      </c>
-      <c r="K11" s="33" t="inlineStr">
-        <is>
-          <t>④ 個別方式は，各ゾーンでの独立運転が容易である。</t>
-        </is>
-      </c>
-      <c r="L11" s="33" t="inlineStr">
-        <is>
-          <t>⑤ 全空気方式は，水方式に比べてダクト寸法を極めて小さくできる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="46" t="inlineStr">
-        <is>
-          <t>R1本-11</t>
-        </is>
-      </c>
-      <c r="B12" s="46" t="inlineStr">
-        <is>
-          <t>Ⅲ-11</t>
-        </is>
-      </c>
-      <c r="C12" s="46" t="inlineStr">
-        <is>
-          <t>建築環境・設備・建築物衛生管理</t>
-        </is>
-      </c>
-      <c r="D12" s="46" t="inlineStr">
-        <is>
-          <t>省エネルギーシステム・BEMS</t>
-        </is>
-      </c>
-      <c r="E12" s="47" t="n">
-        <v>4</v>
-      </c>
-      <c r="F12" s="48" t="inlineStr">
-        <is>
-          <t>建築環境・空調・給排水における技術基準および正誤判定</t>
-        </is>
-      </c>
-      <c r="G12" s="48" t="inlineStr">
-        <is>
-          <t>空調省エネ技術に関する次の記述のうち，最も不適切なものはどれか。</t>
-        </is>
-      </c>
-      <c r="H12" s="48" t="inlineStr">
-        <is>
-          <t>① 全熱交換器は，排気の熱と湿度を回収する。</t>
-        </is>
-      </c>
-      <c r="I12" s="48" t="inlineStr">
-        <is>
-          <t>② 外気冷房は，中間期等の冷涼な外気を冷房に利用する。</t>
-        </is>
-      </c>
-      <c r="J12" s="48" t="inlineStr">
-        <is>
-          <t>③ VWVシステムは，冷温水流量をインバータ制御する。</t>
-        </is>
-      </c>
-      <c r="K12" s="48" t="inlineStr">
-        <is>
-          <t>④ BEMSは，手動バルブの開閉のみを記録する簡易記録計である。</t>
-        </is>
-      </c>
-      <c r="L12" s="48" t="inlineStr">
-        <is>
-          <t>⑤ 蓄熱システムは，夜間電力を利用して熱エネルギーを蓄える。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="32" t="inlineStr">
-        <is>
-          <t>R1本-12</t>
-        </is>
-      </c>
-      <c r="B13" s="32" t="inlineStr">
-        <is>
-          <t>Ⅲ-12</t>
-        </is>
-      </c>
-      <c r="C13" s="32" t="inlineStr">
-        <is>
-          <t>建築環境・設備・建築物衛生管理</t>
-        </is>
-      </c>
-      <c r="D13" s="32" t="inlineStr">
-        <is>
-          <t>給水設備・給水圧力</t>
-        </is>
-      </c>
-      <c r="E13" s="42" t="n">
-        <v>3</v>
-      </c>
-      <c r="F13" s="33" t="inlineStr">
-        <is>
-          <t>建築環境・空調・給排水における技術基準および正誤判定</t>
-        </is>
-      </c>
-      <c r="G13" s="33" t="inlineStr">
-        <is>
-          <t>給水設備に関する次の記述のうち，最も不適切なものはどれか。</t>
-        </is>
-      </c>
-      <c r="H13" s="33" t="inlineStr">
-        <is>
-          <t>① 直結増圧方式は受水槽を置かずに直接給水する。</t>
-        </is>
-      </c>
-      <c r="I13" s="33" t="inlineStr">
-        <is>
-          <t>② クロスコネクションは飲用配管と他系統の誤接続で禁止されている。</t>
-        </is>
-      </c>
-      <c r="J13" s="33" t="inlineStr">
-        <is>
-          <t>③ ウォーターハンマーは静かな流速変化時に発生する現象である。</t>
-        </is>
-      </c>
-      <c r="K13" s="33" t="inlineStr">
-        <is>
-          <t>④ バキュームブレーカは逆流（サイホン作用）を防ぐ。</t>
-        </is>
-      </c>
-      <c r="L13" s="33" t="inlineStr">
-        <is>
-          <t>⑤ 吐水口空間は，給水栓と水受けあふれ面との間の空間である。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="46" t="inlineStr">
-        <is>
-          <t>R1本-13</t>
-        </is>
-      </c>
-      <c r="B14" s="46" t="inlineStr">
-        <is>
-          <t>Ⅲ-13</t>
-        </is>
-      </c>
-      <c r="C14" s="46" t="inlineStr">
-        <is>
-          <t>建築環境・設備・建築物衛生管理</t>
-        </is>
-      </c>
-      <c r="D14" s="46" t="inlineStr">
-        <is>
-          <t>排水・通気配管・トラップ</t>
-        </is>
-      </c>
-      <c r="E14" s="47" t="n">
-        <v>3</v>
-      </c>
-      <c r="F14" s="48" t="inlineStr">
-        <is>
-          <t>建築環境・空調・給排水における技術基準および正誤判定</t>
-        </is>
-      </c>
-      <c r="G14" s="48" t="inlineStr">
-        <is>
-          <t>排水通気設備に関する次の記述のうち，最も不適切なものはどれか。</t>
-        </is>
-      </c>
-      <c r="H14" s="48" t="inlineStr">
-        <is>
-          <t>① トラップの封水深は 50〜100mm である。</t>
-        </is>
-      </c>
-      <c r="I14" s="48" t="inlineStr">
-        <is>
-          <t>② 自己サイホン作用は満管流排水により生じる。</t>
-        </is>
-      </c>
-      <c r="J14" s="48" t="inlineStr">
-        <is>
-          <t>③ 通気管の主な目的は配管を保温して結露を防ぐことのみである。</t>
-        </is>
-      </c>
-      <c r="K14" s="48" t="inlineStr">
-        <is>
-          <t>④ 各個通気方式は，最も高い通気性能をもつ。</t>
-        </is>
-      </c>
-      <c r="L14" s="48" t="inlineStr">
-        <is>
-          <t>⑤ 二重トラップは排水障害を起こすため禁じられる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="32" t="inlineStr">
-        <is>
-          <t>R1本-14</t>
-        </is>
-      </c>
-      <c r="B15" s="32" t="inlineStr">
-        <is>
-          <t>Ⅲ-14</t>
-        </is>
-      </c>
-      <c r="C15" s="32" t="inlineStr">
-        <is>
-          <t>建築環境・設備・建築物衛生管理</t>
-        </is>
-      </c>
-      <c r="D15" s="32" t="inlineStr">
-        <is>
-          <t>封水損失・排水設備</t>
-        </is>
-      </c>
-      <c r="E15" s="42" t="n">
-        <v>5</v>
-      </c>
-      <c r="F15" s="33" t="inlineStr">
-        <is>
-          <t>建築環境・空調・給排水における技術基準および正誤判定</t>
-        </is>
-      </c>
-      <c r="G15" s="33" t="inlineStr">
-        <is>
-          <t>排水配管に関する次の記述のうち，最も不適切なものはどれか。</t>
-        </is>
-      </c>
-      <c r="H15" s="33" t="inlineStr">
-        <is>
-          <t>① 間接排水は衛生上重要な機器の排水口に適用される。</t>
-        </is>
-      </c>
-      <c r="I15" s="33" t="inlineStr">
-        <is>
-          <t>② 排水槽の底には勾配を設けて汚泥滞留を防ぐ。</t>
-        </is>
-      </c>
-      <c r="J15" s="33" t="inlineStr">
-        <is>
-          <t>③ グリーストラップは油脂分を捕集する。</t>
-        </is>
-      </c>
-      <c r="K15" s="33" t="inlineStr">
-        <is>
-          <t>④ 排水横管には適切な勾配を確保する。</t>
-        </is>
-      </c>
-      <c r="L15" s="33" t="inlineStr">
-        <is>
-          <t>⑤ 雨水管と汚水管は建物のすべての場所で合流接続する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="46" t="inlineStr">
-        <is>
-          <t>R1本-15</t>
-        </is>
-      </c>
-      <c r="B16" s="46" t="inlineStr">
-        <is>
-          <t>Ⅲ-15</t>
-        </is>
-      </c>
-      <c r="C16" s="46" t="inlineStr">
-        <is>
-          <t>建築環境・設備・建築物衛生管理</t>
-        </is>
-      </c>
-      <c r="D16" s="46" t="inlineStr">
-        <is>
-          <t>換気方式・換気量</t>
-        </is>
-      </c>
-      <c r="E16" s="47" t="n">
-        <v>2</v>
-      </c>
-      <c r="F16" s="48" t="inlineStr">
-        <is>
-          <t>建物開口部や室温差・風力による換気量・換気回数計算および給排気方式の正誤判定</t>
-        </is>
-      </c>
-      <c r="G16" s="48" t="inlineStr">
-        <is>
-          <t>換気計算及び給排気に関する次の記述のうち，最も不適切なものはどれか。</t>
-        </is>
-      </c>
-      <c r="H16" s="48" t="inlineStr">
-        <is>
-          <t>① 必要換気量は CO2 発生量等から計算できる。</t>
-        </is>
-      </c>
-      <c r="I16" s="48" t="inlineStr">
-        <is>
-          <t>② 第2種換気は，排気ファンのみを用いて室内を負圧にする。</t>
-        </is>
-      </c>
-      <c r="J16" s="48" t="inlineStr">
-        <is>
-          <t>③ 第3種換気は，厨房やトイレ等の汚染・臭気源に適する。</t>
-        </is>
-      </c>
-      <c r="K16" s="48" t="inlineStr">
-        <is>
-          <t>④ 温度差換気量は，高低差と温度差に依存する。</t>
-        </is>
-      </c>
-      <c r="L16" s="48" t="inlineStr">
-        <is>
-          <t>⑤ 風力換気量は，風速と開口面積に比例する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="32" t="inlineStr">
-        <is>
-          <t>R1本-16</t>
-        </is>
-      </c>
-      <c r="B17" s="32" t="inlineStr">
-        <is>
-          <t>Ⅲ-16</t>
-        </is>
-      </c>
-      <c r="C17" s="32" t="inlineStr">
-        <is>
-          <t>建築環境・設備・建築物衛生管理</t>
-        </is>
-      </c>
-      <c r="D17" s="32" t="inlineStr">
-        <is>
-          <t>オゾン・室内空気質</t>
-        </is>
-      </c>
-      <c r="E17" s="42" t="n">
-        <v>2</v>
-      </c>
-      <c r="F17" s="33" t="inlineStr">
-        <is>
-          <t>建築環境・空調・給排水における技術基準および正誤判定</t>
-        </is>
-      </c>
-      <c r="G17" s="33" t="inlineStr">
-        <is>
-          <t>室内有害ガスに関する次の記述のうち，最も不適切なものはどれか。</t>
-        </is>
-      </c>
-      <c r="H17" s="33" t="inlineStr">
-        <is>
-          <t>① CO（一酸化炭素）は，中毒を引き起こす有害ガスである。</t>
-        </is>
-      </c>
-      <c r="I17" s="33" t="inlineStr">
-        <is>
-          <t>② CO2 は，有毒ガスであり微量でも即死に至る。</t>
-        </is>
-      </c>
-      <c r="J17" s="33" t="inlineStr">
-        <is>
-          <t>③ ホルムアルデヒドは，建材や接着剤から放散される。</t>
-        </is>
-      </c>
-      <c r="K17" s="33" t="inlineStr">
-        <is>
-          <t>④ ラドンは，自然放射性物質である。</t>
-        </is>
-      </c>
-      <c r="L17" s="33" t="inlineStr">
-        <is>
-          <t>⑤ 浮遊粉塵は，呼吸器に及ぼす影響が懸念される。</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="46" t="inlineStr">
-        <is>
-          <t>R1本-17</t>
-        </is>
-      </c>
-      <c r="B18" s="46" t="inlineStr">
-        <is>
-          <t>Ⅲ-17</t>
-        </is>
-      </c>
-      <c r="C18" s="46" t="inlineStr">
-        <is>
-          <t>建築環境・設備・建築物衛生管理</t>
-        </is>
-      </c>
-      <c r="D18" s="46" t="inlineStr">
-        <is>
-          <t>ホルムアルデヒド放散速度・濃度</t>
-        </is>
-      </c>
-      <c r="E18" s="47" t="n">
-        <v>3</v>
-      </c>
-      <c r="F18" s="48" t="inlineStr">
-        <is>
-          <t>建築環境・空調・給排水における技術基準および正誤判定</t>
-        </is>
-      </c>
-      <c r="G18" s="48" t="inlineStr">
-        <is>
-          <t>建築物衛生法基準に関する次の記述のうち，最も不適切なものはどれか。</t>
-        </is>
-      </c>
-      <c r="H18" s="48" t="inlineStr">
-        <is>
-          <t>① 浮遊粉塵は 0.15 mg/m3 以下である。</t>
-        </is>
-      </c>
-      <c r="I18" s="48" t="inlineStr">
-        <is>
-          <t>② 一酸化炭素は 10 ppm（特例20ppm）以下である。</t>
-        </is>
-      </c>
-      <c r="J18" s="48" t="inlineStr">
-        <is>
-          <t>③ 二酸化炭素は 10000 ppm 以下である。</t>
-        </is>
-      </c>
-      <c r="K18" s="48" t="inlineStr">
-        <is>
-          <t>④ 気流は 0.5 m/s 以下である。</t>
-        </is>
-      </c>
-      <c r="L18" s="48" t="inlineStr">
-        <is>
-          <t>⑤ 温度・湿度の望ましい範囲が設定されている。</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="32" t="inlineStr">
-        <is>
-          <t>R1本-18</t>
-        </is>
-      </c>
-      <c r="B19" s="32" t="inlineStr">
-        <is>
-          <t>Ⅲ-18</t>
-        </is>
-      </c>
-      <c r="C19" s="32" t="inlineStr">
-        <is>
-          <t>水質管理</t>
-        </is>
-      </c>
-      <c r="D19" s="32" t="inlineStr">
-        <is>
-          <t>BOD測定・BOD容積負荷計算</t>
-        </is>
-      </c>
-      <c r="E19" s="42" t="n">
-        <v>3</v>
-      </c>
-      <c r="F19" s="33" t="inlineStr">
-        <is>
-          <t>流入水量・BOD濃度・ばっ気槽容量に基づくBOD容積負荷およびHRT/BOD-MLSS負荷の定型計算</t>
-        </is>
-      </c>
-      <c r="G19" s="33" t="inlineStr">
-        <is>
-          <t>水質濁度・汚濁指標に関する次の記述のうち，最も不適切なものはどれか。</t>
-        </is>
-      </c>
-      <c r="H19" s="33" t="inlineStr">
-        <is>
-          <t>① BOD は好気性微生物による酸素消費量である。</t>
-        </is>
-      </c>
-      <c r="I19" s="33" t="inlineStr">
-        <is>
-          <t>② COD は化学酸化剤による酸素要求量である。</t>
-        </is>
-      </c>
-      <c r="J19" s="33" t="inlineStr">
-        <is>
-          <t>③ SS は溶解しているすべての塩分濃度を示す。</t>
-        </is>
-      </c>
-      <c r="K19" s="33" t="inlineStr">
-        <is>
-          <t>④ TOC は全有機炭素量である。</t>
-        </is>
-      </c>
-      <c r="L19" s="33" t="inlineStr">
-        <is>
-          <t>⑤ BOD/COD比は生物分解性の目安となる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="46" t="inlineStr">
-        <is>
-          <t>R1本-19</t>
-        </is>
-      </c>
-      <c r="B20" s="46" t="inlineStr">
-        <is>
-          <t>Ⅲ-19</t>
-        </is>
-      </c>
-      <c r="C20" s="46" t="inlineStr">
-        <is>
-          <t>水質管理</t>
-        </is>
-      </c>
-      <c r="D20" s="46" t="inlineStr">
-        <is>
-          <t>水質測定項目・測定方法</t>
-        </is>
-      </c>
-      <c r="E20" s="47" t="n">
-        <v>4</v>
-      </c>
-      <c r="F20" s="48" t="inlineStr">
-        <is>
-          <t>水質汚濁防止・汚水処理技術および水質試験方法に関する正誤判定</t>
-        </is>
-      </c>
-      <c r="G20" s="48" t="inlineStr">
-        <is>
-          <t>水質分析に関する次の記述のうち，最も不適切なものはどれか。</t>
-        </is>
-      </c>
-      <c r="H20" s="48" t="inlineStr">
-        <is>
-          <t>① BOD5 は 20℃ で 5 日間培養して測定する。</t>
-        </is>
-      </c>
-      <c r="I20" s="48" t="inlineStr">
-        <is>
-          <t>② DO 測定には電極法やウィンクラー法が用いられる。</t>
-        </is>
-      </c>
-      <c r="J20" s="48" t="inlineStr">
-        <is>
-          <t>③ 濁度は水の濁り具合を示す。</t>
-        </is>
-      </c>
-      <c r="K20" s="48" t="inlineStr">
-        <is>
-          <t>④ 大腸菌群数は，顕微鏡で全細胞数を目視で直数カウントするのみである。</t>
-        </is>
-      </c>
-      <c r="L20" s="48" t="inlineStr">
-        <is>
-          <t>⑤ 吸光光度法は微量成分分析に汎用される。</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="32" t="inlineStr">
-        <is>
-          <t>R1本-20</t>
-        </is>
-      </c>
-      <c r="B21" s="32" t="inlineStr">
-        <is>
-          <t>Ⅲ-20</t>
-        </is>
-      </c>
-      <c r="C21" s="32" t="inlineStr">
-        <is>
-          <t>水質管理</t>
-        </is>
-      </c>
-      <c r="D21" s="32" t="inlineStr">
-        <is>
-          <t>各種活性汚泥法(膜分離/嫌気好気等)</t>
-        </is>
-      </c>
-      <c r="E21" s="42" t="n">
-        <v>5</v>
-      </c>
-      <c r="F21" s="33" t="inlineStr">
-        <is>
-          <t>標準活性汚泥法、膜分離(MBR)、A2O法、ステップエアレーション等の特徴と運転条件の比較</t>
-        </is>
-      </c>
-      <c r="G21" s="33" t="inlineStr">
-        <is>
-          <t>生物処理に関する次の記述のうち，最も不適切なものはどれか。</t>
-        </is>
-      </c>
-      <c r="H21" s="33" t="inlineStr">
-        <is>
-          <t>① 標準活性汚泥法はばっ気槽と沈殿池で構成される。</t>
-        </is>
-      </c>
-      <c r="I21" s="33" t="inlineStr">
-        <is>
-          <t>② A2O法は窒素とリンを同時に除去する。</t>
-        </is>
-      </c>
-      <c r="J21" s="33" t="inlineStr">
-        <is>
-          <t>③ MBRは膜で固液分離を行う。</t>
-        </is>
-      </c>
-      <c r="K21" s="33" t="inlineStr">
-        <is>
-          <t>④ 回転円板法は固定膜方式の一種である。</t>
-        </is>
-      </c>
-      <c r="L21" s="33" t="inlineStr">
-        <is>
-          <t>⑤ 硝化反応は完全な嫌気性条件下でのみ進行する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="46" t="inlineStr">
-        <is>
-          <t>R1本-21</t>
-        </is>
-      </c>
-      <c r="B22" s="46" t="inlineStr">
-        <is>
-          <t>Ⅲ-21</t>
-        </is>
-      </c>
-      <c r="C22" s="46" t="inlineStr">
-        <is>
-          <t>水質管理</t>
-        </is>
-      </c>
-      <c r="D22" s="46" t="inlineStr">
-        <is>
-          <t>浄化槽の構造・処理方式</t>
-        </is>
-      </c>
-      <c r="E22" s="47" t="n">
-        <v>2</v>
-      </c>
-      <c r="F22" s="48" t="inlineStr">
-        <is>
-          <t>浄化槽法および構造基準に基づく各種処理方式（単独・合併）、保守点検・清掃頻度の正誤判定</t>
-        </is>
-      </c>
-      <c r="G22" s="48" t="inlineStr">
-        <is>
-          <t>浄化槽に関する次の記述のうち，最も不適切なものはどれか。</t>
-        </is>
-      </c>
-      <c r="H22" s="48" t="inlineStr">
-        <is>
-          <t>① 合併処理浄化槽はし尿と雑排水を処理する。</t>
-        </is>
-      </c>
-      <c r="I22" s="48" t="inlineStr">
-        <is>
-          <t>② 単独処理浄化槽は，環境負荷が小さいため今後の設置が推奨されている。</t>
-        </is>
-      </c>
-      <c r="J22" s="48" t="inlineStr">
-        <is>
-          <t>③ 法定検査の義務が定められている。</t>
-        </is>
-      </c>
-      <c r="K22" s="48" t="inlineStr">
-        <is>
-          <t>④ 保守点検や清掃が定期的に必要である。</t>
-        </is>
-      </c>
-      <c r="L22" s="48" t="inlineStr">
-        <is>
-          <t>⑤ 消毒工程を経て放流される。</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="32" t="inlineStr">
-        <is>
-          <t>R1本-22</t>
-        </is>
-      </c>
-      <c r="B23" s="32" t="inlineStr">
-        <is>
-          <t>Ⅲ-22</t>
-        </is>
-      </c>
-      <c r="C23" s="32" t="inlineStr">
-        <is>
-          <t>水質管理</t>
-        </is>
-      </c>
-      <c r="D23" s="32" t="inlineStr">
-        <is>
-          <t>汚泥の含水率・濃縮計算</t>
-        </is>
-      </c>
-      <c r="E23" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" s="33" t="inlineStr">
-        <is>
-          <t>汚泥の含水率変化に伴う汚泥発生量・濃縮量の定型計算および沈降特性(SVI)に関する正誤判定</t>
-        </is>
-      </c>
-      <c r="G23" s="33" t="inlineStr">
-        <is>
-          <t>汚泥処理に関する次の記述のうち，最も不適切なものはどれか。</t>
-        </is>
-      </c>
-      <c r="H23" s="33" t="inlineStr">
-        <is>
-          <t>① 汚泥濃縮を行っても，汚泥の体積は全く変化しない。</t>
-        </is>
-      </c>
-      <c r="I23" s="33" t="inlineStr">
-        <is>
-          <t>② 嫌気性消化により発酵ガス（メタン）が得られる。</t>
-        </is>
-      </c>
-      <c r="J23" s="33" t="inlineStr">
-        <is>
-          <t>③ 凝集剤の添加は脱水性を改善する。</t>
-        </is>
-      </c>
-      <c r="K23" s="33" t="inlineStr">
-        <is>
-          <t>④ 焼却処理は減容化に効果的である。</t>
-        </is>
-      </c>
-      <c r="L23" s="33" t="inlineStr">
-        <is>
-          <t>⑤ 遠心脱水機やベルトプレスが用いられる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="46" t="inlineStr">
-        <is>
-          <t>R1本-23</t>
-        </is>
-      </c>
-      <c r="B24" s="46" t="inlineStr">
-        <is>
-          <t>Ⅲ-23</t>
-        </is>
-      </c>
-      <c r="C24" s="46" t="inlineStr">
-        <is>
-          <t>水質管理</t>
-        </is>
-      </c>
-      <c r="D24" s="46" t="inlineStr">
-        <is>
-          <t>BOD/COD環境基準達成率</t>
-        </is>
-      </c>
-      <c r="E24" s="47" t="n">
-        <v>4</v>
-      </c>
-      <c r="F24" s="48" t="inlineStr">
-        <is>
-          <t>流入水量・BOD濃度・ばっ気槽容量に基づくBOD容積負荷およびHRT/BOD-MLSS負荷の定型計算</t>
-        </is>
-      </c>
-      <c r="G24" s="48" t="inlineStr">
-        <is>
-          <t>水質環境基準に関する次の記述のうち，最も不適切なものはどれか。</t>
-        </is>
-      </c>
-      <c r="H24" s="48" t="inlineStr">
-        <is>
-          <t>① 河川には BOD 基準が設定されている。</t>
-        </is>
-      </c>
-      <c r="I24" s="48" t="inlineStr">
-        <is>
-          <t>② 湖沼には COD 基準が設定されている。</t>
-        </is>
-      </c>
-      <c r="J24" s="48" t="inlineStr">
-        <is>
-          <t>③ 富栄養化対策として窒素・リンの基準がある。</t>
-        </is>
-      </c>
-      <c r="K24" s="48" t="inlineStr">
-        <is>
-          <t>④ 健康項目は，基準超過が日常的に全国で多発している。</t>
-        </is>
-      </c>
-      <c r="L24" s="48" t="inlineStr">
-        <is>
-          <t>⑤ 水生生物の保全に関する基準が設けられている。</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="32" t="inlineStr">
-        <is>
-          <t>R1本-24</t>
-        </is>
-      </c>
-      <c r="B25" s="32" t="inlineStr">
-        <is>
-          <t>Ⅲ-24</t>
-        </is>
-      </c>
-      <c r="C25" s="32" t="inlineStr">
-        <is>
-          <t>水質管理</t>
-        </is>
-      </c>
-      <c r="D25" s="32" t="inlineStr">
-        <is>
-          <t>水質汚濁防止法排水基準</t>
-        </is>
-      </c>
-      <c r="E25" s="42" t="n">
-        <v>4</v>
-      </c>
-      <c r="F25" s="33" t="inlineStr">
-        <is>
-          <t>水質汚濁防止・汚水処理技術および水質試験方法に関する正誤判定</t>
-        </is>
-      </c>
-      <c r="G25" s="33" t="inlineStr">
-        <is>
-          <t>水質汚濁防止法に関する次の記述のうち，最も不適切なものはどれか。</t>
-        </is>
-      </c>
-      <c r="H25" s="33" t="inlineStr">
-        <is>
-          <t>① 特定施設からの排出水に規制が適用される。</t>
-        </is>
-      </c>
-      <c r="I25" s="33" t="inlineStr">
-        <is>
-          <t>② 都道府県は上乗せ基準を設定できる。</t>
-        </is>
-      </c>
-      <c r="J25" s="33" t="inlineStr">
-        <is>
-          <t>③ 有害物質の地下浸透規制がある。</t>
-        </is>
-      </c>
-      <c r="K25" s="33" t="inlineStr">
-        <is>
-          <t>④ 事故時の措置や届出義務は完全免除されている。</t>
-        </is>
-      </c>
-      <c r="L25" s="33" t="inlineStr">
-        <is>
-          <t>⑤ 指定水域での総量規制が適用される。</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="46" t="inlineStr">
-        <is>
-          <t>R1本-25</t>
-        </is>
-      </c>
-      <c r="B26" s="46" t="inlineStr">
-        <is>
-          <t>Ⅲ-25</t>
-        </is>
-      </c>
-      <c r="C26" s="46" t="inlineStr">
-        <is>
-          <t>水質管理</t>
-        </is>
-      </c>
-      <c r="D26" s="46" t="inlineStr">
-        <is>
-          <t>消毒(塩素/オゾン/紫外線)</t>
-        </is>
-      </c>
-      <c r="E26" s="47" t="n">
-        <v>3</v>
-      </c>
-      <c r="F26" s="48" t="inlineStr">
-        <is>
-          <t>遊離残留塩素、結合残留塩素（クロラミン）、オゾン、紫外線消毒の殺菌力・残留性比較</t>
-        </is>
-      </c>
-      <c r="G26" s="48" t="inlineStr">
-        <is>
-          <t>水処理における消毒技術に関する次の記述のうち，最も不適切なものはどれか。</t>
-        </is>
-      </c>
-      <c r="H26" s="48" t="inlineStr">
-        <is>
-          <t>① 塩素消毒は，残留効果（残留塩素）をもつ利点がある。</t>
-        </is>
-      </c>
-      <c r="I26" s="48" t="inlineStr">
-        <is>
-          <t>② 結合残留塩素（クロラミン）は，遊離残留塩素に比べて殺菌力が遅いが持続性がある。</t>
-        </is>
-      </c>
-      <c r="J26" s="48" t="inlineStr">
-        <is>
-          <t>③ 紫外線（UV）消毒は，強い残留効果が長時間維持されるため，配管網の末端消毒に最適である。</t>
-        </is>
-      </c>
-      <c r="K26" s="48" t="inlineStr">
-        <is>
-          <t>④ オゾン消毒は，強力な酸化力をもつが，水中の残留性が低いため末端補強が必要となる。</t>
-        </is>
-      </c>
-      <c r="L26" s="48" t="inlineStr">
-        <is>
-          <t>⑤ トリハロメタン（THM）は，塩素と水中の有機物が反応して生じる副生成物である。</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="32" t="inlineStr">
-        <is>
-          <t>R1本-26</t>
-        </is>
-      </c>
-      <c r="B27" s="32" t="inlineStr">
-        <is>
-          <t>Ⅲ-26</t>
-        </is>
-      </c>
-      <c r="C27" s="32" t="inlineStr">
-        <is>
-          <t>水質管理</t>
-        </is>
-      </c>
-      <c r="D27" s="32" t="inlineStr">
-        <is>
-          <t>硝化・脱窒反応</t>
-        </is>
-      </c>
-      <c r="E27" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="F27" s="33" t="inlineStr">
-        <is>
-          <t>水質汚濁防止・汚水処理技術および水質試験方法に関する正誤判定</t>
-        </is>
-      </c>
-      <c r="G27" s="33" t="inlineStr">
-        <is>
-          <t>窒素除去反応に関する次の記述のうち，最も不適切なものはどれか。</t>
-        </is>
-      </c>
-      <c r="H27" s="33" t="inlineStr">
-        <is>
-          <t>① 硝化反応は，無酸素条件下で進行する還元反応である。</t>
-        </is>
-      </c>
-      <c r="I27" s="33" t="inlineStr">
-        <is>
-          <t>② 硝化菌（亜硝酸菌・硝酸菌）は好気性独立栄養細菌である。</t>
-        </is>
-      </c>
-      <c r="J27" s="33" t="inlineStr">
-        <is>
-          <t>③ 脱窒反応は，無酸素条件（通気なし）で脱窒菌により進行する。</t>
-        </is>
-      </c>
-      <c r="K27" s="33" t="inlineStr">
-        <is>
-          <t>④ 脱窒反応では有機物（炭素源）が消費される。</t>
-        </is>
-      </c>
-      <c r="L27" s="33" t="inlineStr">
-        <is>
-          <t>⑤ 脱窒により窒素ガス（N2）として気体放出される。</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="46" t="inlineStr">
-        <is>
-          <t>R1本-27</t>
-        </is>
-      </c>
-      <c r="B28" s="46" t="inlineStr">
-        <is>
-          <t>Ⅲ-27</t>
-        </is>
-      </c>
-      <c r="C28" s="46" t="inlineStr">
-        <is>
-          <t>水質管理</t>
-        </is>
-      </c>
-      <c r="D28" s="46" t="inlineStr">
-        <is>
-          <t>DO測定法・大腸菌数測定</t>
-        </is>
-      </c>
-      <c r="E28" s="47" t="n">
-        <v>2</v>
-      </c>
-      <c r="F28" s="48" t="inlineStr">
-        <is>
-          <t>水質汚濁防止・汚水処理技術および水質試験方法に関する正誤判定</t>
-        </is>
-      </c>
-      <c r="G28" s="48" t="inlineStr">
-        <is>
-          <t>水質測定手法に関する次の記述のうち，最も不適切なものはどれか。</t>
-        </is>
-      </c>
-      <c r="H28" s="48" t="inlineStr">
-        <is>
-          <t>① ウィンクラー法は，溶存酸素（DO）の滴定測定法である。</t>
-        </is>
-      </c>
-      <c r="I28" s="48" t="inlineStr">
-        <is>
-          <t>② DOメーター（電極法）は，測定に数日間の培養時間を要する。</t>
-        </is>
-      </c>
-      <c r="J28" s="48" t="inlineStr">
-        <is>
-          <t>③ 最確数法（MPN法）は大腸菌群数の測定に用いられる。</t>
-        </is>
-      </c>
-      <c r="K28" s="48" t="inlineStr">
-        <is>
-          <t>④ 検知管法はガスの簡易測定に適している。</t>
-        </is>
-      </c>
-      <c r="L28" s="48" t="inlineStr">
-        <is>
-          <t>⑤ フレーム原子吸光法は金属元素分析に用いられる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="32" t="inlineStr">
-        <is>
-          <t>R1本-28</t>
-        </is>
-      </c>
-      <c r="B29" s="32" t="inlineStr">
-        <is>
-          <t>Ⅲ-28</t>
-        </is>
-      </c>
-      <c r="C29" s="32" t="inlineStr">
-        <is>
-          <t>水質管理</t>
-        </is>
-      </c>
-      <c r="D29" s="32" t="inlineStr">
-        <is>
-          <t>BOD測定・BOD容積負荷計算</t>
-        </is>
-      </c>
-      <c r="E29" s="42" t="n">
-        <v>5</v>
-      </c>
-      <c r="F29" s="33" t="inlineStr">
-        <is>
-          <t>流入水量・BOD濃度・ばっ気槽容量に基づくBOD容積負荷およびHRT/BOD-MLSS負荷の定型計算</t>
-        </is>
-      </c>
-      <c r="G29" s="33" t="inlineStr">
-        <is>
-          <t>下水処理場の管理指標に関する次の記述のうち，最も不適切なものはどれか。</t>
-        </is>
-      </c>
-      <c r="H29" s="33" t="inlineStr">
-        <is>
-          <t>① BOD容積負荷は，ばっ気槽単位容積当たりの日BOD流入量である。</t>
-        </is>
-      </c>
-      <c r="I29" s="33" t="inlineStr">
-        <is>
-          <t>② BOD-SS負荷は，活性汚泥量に対するBOD負荷量を示す。</t>
-        </is>
-      </c>
-      <c r="J29" s="33" t="inlineStr">
-        <is>
-          <t>③ 水力学的滞留時間（HRT）は，槽容積を流入水量で除した値である。</t>
-        </is>
-      </c>
-      <c r="K29" s="33" t="inlineStr">
-        <is>
-          <t>④ SVI は，汚泥の沈降濃縮性を示す指標である。</t>
-        </is>
-      </c>
-      <c r="L29" s="33" t="inlineStr">
-        <is>
-          <t>⑤ SVI が 200 以上と高くなると，汚泥沈降性が極めて良好になる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="46" t="inlineStr">
-        <is>
-          <t>R1本-29</t>
-        </is>
-      </c>
-      <c r="B30" s="46" t="inlineStr">
-        <is>
-          <t>Ⅲ-29</t>
-        </is>
-      </c>
-      <c r="C30" s="46" t="inlineStr">
-        <is>
-          <t>水質管理</t>
-        </is>
-      </c>
-      <c r="D30" s="46" t="inlineStr">
-        <is>
-          <t>水質測定項目・測定方法</t>
-        </is>
-      </c>
-      <c r="E30" s="47" t="n">
-        <v>2</v>
-      </c>
-      <c r="F30" s="48" t="inlineStr">
-        <is>
-          <t>水質汚濁防止・汚水処理技術および水質試験方法に関する正誤判定</t>
-        </is>
-      </c>
-      <c r="G30" s="48" t="inlineStr">
-        <is>
-          <t>下水管渠及び処理施設に関する次の記述のうち，最も不適切なものはどれか。</t>
-        </is>
-      </c>
-      <c r="H30" s="48" t="inlineStr">
-        <is>
-          <t>① 分流式下水道は，汚水と雨水を別々の管渠で排除する。</t>
-        </is>
-      </c>
-      <c r="I30" s="48" t="inlineStr">
-        <is>
-          <t>② 合流式下水道は，雨水時に未処理汚水が排出されるリスクが一切存在しない完璧なシステムである。</t>
-        </is>
-      </c>
-      <c r="J30" s="48" t="inlineStr">
-        <is>
-          <t>③ 下水管渠内の流速は，固形物の沈殿防止と摩耗防止の観点から適切な範囲に保つ。</t>
-        </is>
-      </c>
-      <c r="K30" s="48" t="inlineStr">
-        <is>
-          <t>④ 最初の沈殿池は，重力沈降によりSSを除去する。</t>
-        </is>
-      </c>
-      <c r="L30" s="48" t="inlineStr">
-        <is>
-          <t>⑤ 最終沈殿池は，活性汚泥を固液分離して上澄水を得る。</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="32" t="inlineStr">
-        <is>
-          <t>R1本-30</t>
-        </is>
-      </c>
-      <c r="B31" s="32" t="inlineStr">
-        <is>
-          <t>Ⅲ-30</t>
-        </is>
-      </c>
-      <c r="C31" s="32" t="inlineStr">
-        <is>
-          <t>水質管理</t>
-        </is>
-      </c>
-      <c r="D31" s="32" t="inlineStr">
-        <is>
-          <t>各種活性汚泥法(膜分離/嫌気好気等)</t>
-        </is>
-      </c>
-      <c r="E31" s="42" t="n">
-        <v>3</v>
-      </c>
-      <c r="F31" s="33" t="inlineStr">
-        <is>
-          <t>標準活性汚泥法、膜分離(MBR)、A2O法、ステップエアレーション等の特徴と運転条件の比較</t>
-        </is>
-      </c>
-      <c r="G31" s="33" t="inlineStr">
-        <is>
-          <t>高度処理技術に関する次の記述のうち，最も不適切なものはどれか。</t>
-        </is>
-      </c>
-      <c r="H31" s="33" t="inlineStr">
-        <is>
-          <t>① 凝集加圧浮上法は，微細気泡で浮遊物を浮上分離する。</t>
-        </is>
-      </c>
-      <c r="I31" s="33" t="inlineStr">
-        <is>
-          <t>② 活性炭吸着は，微量有機物や色度・臭気の除去に有効である。</t>
-        </is>
-      </c>
-      <c r="J31" s="33" t="inlineStr">
-        <is>
-          <t>③ 逆浸透（RO）膜は，懸濁粒子のみを通し純水分子を完全に阻止する。</t>
-        </is>
-      </c>
-      <c r="K31" s="33" t="inlineStr">
-        <is>
-          <t>④ オゾン処理は，脱色・脱臭・除菌効果をもつ。</t>
-        </is>
-      </c>
-      <c r="L31" s="33" t="inlineStr">
-        <is>
-          <t>⑤ 膜濾過処理（MF/UF）は，処理水の再利用に寄与する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="46" t="inlineStr">
-        <is>
-          <t>R1本-31</t>
-        </is>
-      </c>
-      <c r="B32" s="46" t="inlineStr">
-        <is>
-          <t>Ⅲ-31</t>
-        </is>
-      </c>
-      <c r="C32" s="46" t="inlineStr">
-        <is>
-          <t>水質管理</t>
-        </is>
-      </c>
-      <c r="D32" s="46" t="inlineStr">
-        <is>
-          <t>浄化槽の構造・処理方式</t>
-        </is>
-      </c>
-      <c r="E32" s="47" t="n">
-        <v>3</v>
-      </c>
-      <c r="F32" s="48" t="inlineStr">
-        <is>
-          <t>浄化槽法および構造基準に基づく各種処理方式（単独・合併）、保守点検・清掃頻度の正誤判定</t>
-        </is>
-      </c>
-      <c r="G32" s="48" t="inlineStr">
-        <is>
-          <t>浄化槽の維持管理に関する次の記述のうち，最も不適切なものはどれか。</t>
-        </is>
-      </c>
-      <c r="H32" s="48" t="inlineStr">
-        <is>
-          <t>① 保守点検は，機器調整や消毒剤補給などを行う。</t>
-        </is>
-      </c>
-      <c r="I32" s="48" t="inlineStr">
-        <is>
-          <t>② 清掃は，汚泥の引き抜きや調整等を行う。</t>
-        </is>
-      </c>
-      <c r="J32" s="48" t="inlineStr">
-        <is>
-          <t>③ 法定検査は，浄化槽清掃業者が自ら合否判定を行う自社検査である。</t>
-        </is>
-      </c>
-      <c r="K32" s="48" t="inlineStr">
-        <is>
-          <t>④ 処理水の放流基準が定められている。</t>
-        </is>
-      </c>
-      <c r="L32" s="48" t="inlineStr">
-        <is>
-          <t>⑤ 浄化槽技術管理者の設置が必要な規模がある。</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="32" t="inlineStr">
-        <is>
-          <t>R1本-32</t>
-        </is>
-      </c>
-      <c r="B33" s="32" t="inlineStr">
-        <is>
-          <t>Ⅲ-32</t>
-        </is>
-      </c>
-      <c r="C33" s="32" t="inlineStr">
-        <is>
-          <t>水質管理</t>
-        </is>
-      </c>
-      <c r="D33" s="32" t="inlineStr">
-        <is>
-          <t>汚泥の含水率・濃縮計算</t>
-        </is>
-      </c>
-      <c r="E33" s="42" t="n">
-        <v>4</v>
-      </c>
-      <c r="F33" s="33" t="inlineStr">
-        <is>
-          <t>汚泥の含水率変化に伴う汚泥発生量・濃縮量の定型計算および沈降特性(SVI)に関する正誤判定</t>
-        </is>
-      </c>
-      <c r="G33" s="33" t="inlineStr">
-        <is>
-          <t>汚泥の脱水・焼却に関する次の記述のうち，最も不適切なものはどれか。</t>
-        </is>
-      </c>
-      <c r="H33" s="33" t="inlineStr">
-        <is>
-          <t>① 濃縮汚泥に凝集剤を添加してフロックを形成させる。</t>
-        </is>
-      </c>
-      <c r="I33" s="33" t="inlineStr">
-        <is>
-          <t>② 脱水ケーキの含水率は 75〜85% 程度となる。</t>
-        </is>
-      </c>
-      <c r="J33" s="33" t="inlineStr">
-        <is>
-          <t>③ 焼却により汚泥中の有機物は分解焼失する。</t>
-        </is>
-      </c>
-      <c r="K33" s="33" t="inlineStr">
-        <is>
-          <t>④ 焼却灰は，すべて無条件に海洋投棄される。</t>
-        </is>
-      </c>
-      <c r="L33" s="33" t="inlineStr">
-        <is>
-          <t>⑤ 脱水機の選定は汚泥性状に応じて行われる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="46" t="inlineStr">
-        <is>
-          <t>R1本-33</t>
-        </is>
-      </c>
-      <c r="B34" s="46" t="inlineStr">
-        <is>
-          <t>Ⅲ-33</t>
-        </is>
-      </c>
-      <c r="C34" s="46" t="inlineStr">
-        <is>
-          <t>水質管理</t>
-        </is>
-      </c>
-      <c r="D34" s="46" t="inlineStr">
-        <is>
-          <t>BOD/COD環境基準達成率</t>
-        </is>
-      </c>
-      <c r="E34" s="47" t="n">
-        <v>2</v>
-      </c>
-      <c r="F34" s="48" t="inlineStr">
-        <is>
-          <t>流入水量・BOD濃度・ばっ気槽容量に基づくBOD容積負荷およびHRT/BOD-MLSS負荷の定型計算</t>
-        </is>
-      </c>
-      <c r="G34" s="48" t="inlineStr">
-        <is>
-          <t>水質汚濁防止対策に関する次の記述のうち，最も不適切なものはどれか。</t>
-        </is>
-      </c>
-      <c r="H34" s="48" t="inlineStr">
-        <is>
-          <t>① 総量削減基本方針に基づき，指定水域の負荷削減が進められる。</t>
-        </is>
-      </c>
-      <c r="I34" s="48" t="inlineStr">
-        <is>
-          <t>② 面源汚染（生活雑排水や農地雨水等）は，一点から集中排出されるため捕捉が非常に容易である。</t>
-        </is>
-      </c>
-      <c r="J34" s="48" t="inlineStr">
-        <is>
-          <t>③ 閉鎖性水域では，富栄養化による赤潮や青潮の発生が問題となる。</t>
-        </is>
-      </c>
-      <c r="K34" s="48" t="inlineStr">
-        <is>
-          <t>④ 下水道の整備は，水質改善に大きく貢献している。</t>
-        </is>
-      </c>
-      <c r="L34" s="48" t="inlineStr">
-        <is>
-          <t>⑤ 底質浄化や浚渫事業も水環境改善に有効である。</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="65" customHeight="1">
-      <c r="A35" s="32" t="inlineStr">
-        <is>
-          <t>R1本-34</t>
-        </is>
-      </c>
-      <c r="B35" s="32" t="inlineStr">
-        <is>
-          <t>Ⅲ-34</t>
-        </is>
-      </c>
-      <c r="C35" s="32" t="inlineStr">
-        <is>
-          <t>水質管理</t>
-        </is>
-      </c>
-      <c r="D35" s="32" t="inlineStr">
-        <is>
-          <t>水質汚濁防止法排水基準</t>
-        </is>
-      </c>
-      <c r="E35" s="42" t="n">
-        <v>5</v>
-      </c>
-      <c r="F35" s="33" t="inlineStr">
-        <is>
-          <t>水質汚濁防止・汚水処理技術および水質試験方法に関する正誤判定</t>
-        </is>
-      </c>
-      <c r="G35" s="33" t="inlineStr">
-        <is>
-          <t>工場排水処理に関する次の記述のうち，最も不適切なものはどれか。</t>
-        </is>
-      </c>
-      <c r="H35" s="33" t="inlineStr">
-        <is>
-          <t>① 中和処理は，酸・アルカリ排水のpHを調整する。</t>
-        </is>
-      </c>
-      <c r="I35" s="33" t="inlineStr">
-        <is>
-          <t>② 凝集沈殿法は，重金属やSSの除去に用いられる。</t>
-        </is>
-      </c>
-      <c r="J35" s="33" t="inlineStr">
-        <is>
-          <t>③ シアン化合物は，高濃度塩素等で分解処理される。</t>
-        </is>
-      </c>
-      <c r="K35" s="33" t="inlineStr">
-        <is>
-          <t>④ 六価クロムは，還元処理して三価クロムにして沈殿させる。</t>
-        </is>
-      </c>
-      <c r="L35" s="33" t="inlineStr">
-        <is>
-          <t>⑤ 油分含有排水は，処理なしでそのまま河川へ放流してよい。</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="65" customHeight="1">
-      <c r="A36" s="46" t="inlineStr">
-        <is>
-          <t>R1本-35</t>
-        </is>
-      </c>
-      <c r="B36" s="46" t="inlineStr">
-        <is>
-          <t>Ⅲ-35</t>
-        </is>
-      </c>
-      <c r="C36" s="46" t="inlineStr">
-        <is>
-          <t>水質管理</t>
-        </is>
-      </c>
-      <c r="D36" s="46" t="inlineStr">
-        <is>
-          <t>消毒(塩素/オゾン/紫外線)</t>
-        </is>
-      </c>
-      <c r="E36" s="47" t="n">
-        <v>5</v>
-      </c>
-      <c r="F36" s="48" t="inlineStr">
-        <is>
-          <t>遊離残留塩素、結合残留塩素（クロラミン）、オゾン、紫外線消毒の殺菌力・残留性比較</t>
-        </is>
-      </c>
-      <c r="G36" s="48" t="inlineStr">
-        <is>
-          <t>水環境保全と持続可能社会に関する次の記述のうち，最も不適切なものはどれか。</t>
-        </is>
-      </c>
-      <c r="H36" s="48" t="inlineStr">
-        <is>
-          <t>① 水循環基本法に基づき，健全な水循環の維持が目指されている。</t>
-        </is>
-      </c>
-      <c r="I36" s="48" t="inlineStr">
-        <is>
-          <t>② 処理水の再利用は，節水及び資源循環に寄与する。</t>
-        </is>
-      </c>
-      <c r="J36" s="48" t="inlineStr">
-        <is>
-          <t>③ 雨水の有効利用（中水道等）が進められている。</t>
-        </is>
-      </c>
-      <c r="K36" s="48" t="inlineStr">
-        <is>
-          <t>④ 下水汚泥のエネルギー利用（メタン発酵・燃料化）が期待されている。</t>
-        </is>
-      </c>
-      <c r="L36" s="48" t="inlineStr">
-        <is>
-          <t>⑤ 水処理プロセスでの電力消費や温室効果ガス排出は地球温暖化と無関係である。</t>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>指定廃棄物の定義基準（8,000Bq/kg）と福島県内除染土壌・指定廃棄物等の中間貯蔵施設保管基準（10万Bq/kg）の穴埋め</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>指定廃棄物に関する次の記述の，［　］に入る数値の組合せとして，最も適切なものはどれか。
+2011年3月に発生した原子力発電所の事故で放射性物質により汚染された廃棄物のうち，［ A ］ベクレル／kgを超えるものを指定廃棄物とし，国の責任のもと，適切な方法で処理することとなっている。また，福島県内で除染に伴い発生した除染土壌や［ B ］ベクレル／kgを超える指定廃棄物等を安全に集中的に管理・保管するために中間貯蔵施設の整備が進められている。</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>① 100 ／ 8,000</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>② 100 ／ 5万</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>③ 1,000 ／ 10万</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>④ 8,000 ／ 5万</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>⑤ 8,000 ／ 10万</t>
         </is>
       </c>
     </row>
